--- a/research/traditional_assets/database/data/oman/oman_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_chemical_basic.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1152685924699146</v>
+        <v>0.1151339395812097</v>
       </c>
       <c r="C2">
-        <v>229.2375546762267</v>
+        <v>227.6409097528601</v>
       </c>
       <c r="D2">
-        <v>227.2575546762267</v>
+        <v>227.6989097528601</v>
       </c>
       <c r="E2">
-        <v>-127.6</v>
+        <v>-125.562</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.038</v>
       </c>
       <c r="G2">
         <v>1.98</v>
@@ -1579,28 +1579,28 @@
         <v>28.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1025114</v>
       </c>
       <c r="N2">
-        <v>28.7</v>
+        <v>28.5974886</v>
       </c>
       <c r="O2">
-        <v>4.305000000000001</v>
+        <v>4.28962329</v>
       </c>
       <c r="P2">
-        <v>24.395</v>
+        <v>24.30786531</v>
       </c>
       <c r="Q2">
-        <v>32.695</v>
+        <v>32.60786531</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1152685924699146</v>
+        <v>0.1158650399810199</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470864</v>
+        <v>0.9131823500886522</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>279.9688619997386</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1151339395812097</v>
+        <v>0.1149992866925049</v>
       </c>
       <c r="C3">
-        <v>227.6409097528601</v>
+        <v>226.0459824696269</v>
       </c>
       <c r="D3">
-        <v>227.6989097528601</v>
+        <v>228.141982469627</v>
       </c>
       <c r="E3">
-        <v>-125.562</v>
+        <v>-123.524</v>
       </c>
       <c r="F3">
-        <v>2.038</v>
+        <v>4.076000000000001</v>
       </c>
       <c r="G3">
         <v>1.98</v>
@@ -1661,28 +1661,28 @@
         <v>28.7</v>
       </c>
       <c r="M3">
-        <v>0.1025114</v>
+        <v>0.2050228</v>
       </c>
       <c r="N3">
-        <v>28.5974886</v>
+        <v>28.4949772</v>
       </c>
       <c r="O3">
-        <v>4.28962329</v>
+        <v>4.274246580000001</v>
       </c>
       <c r="P3">
-        <v>24.30786531</v>
+        <v>24.22073062</v>
       </c>
       <c r="Q3">
-        <v>32.60786531</v>
+        <v>32.52073062</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1158650399810199</v>
+        <v>0.1164736598903111</v>
       </c>
       <c r="T3">
-        <v>0.9131823500886522</v>
+        <v>0.9211147077841277</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>279.9688619997386</v>
+        <v>139.9844309998693</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1149992866925049</v>
+        <v>0.1148646338038</v>
       </c>
       <c r="C4">
-        <v>226.0459824696269</v>
+        <v>224.4527828729949</v>
       </c>
       <c r="D4">
-        <v>228.141982469627</v>
+        <v>228.5867828729949</v>
       </c>
       <c r="E4">
-        <v>-123.524</v>
+        <v>-121.486</v>
       </c>
       <c r="F4">
-        <v>4.076000000000001</v>
+        <v>6.114</v>
       </c>
       <c r="G4">
         <v>1.98</v>
@@ -1743,28 +1743,28 @@
         <v>28.7</v>
       </c>
       <c r="M4">
-        <v>0.2050228</v>
+        <v>0.3075342</v>
       </c>
       <c r="N4">
-        <v>28.4949772</v>
+        <v>28.3924658</v>
       </c>
       <c r="O4">
-        <v>4.274246580000001</v>
+        <v>4.258869870000001</v>
       </c>
       <c r="P4">
-        <v>24.22073062</v>
+        <v>24.13359593</v>
       </c>
       <c r="Q4">
-        <v>32.52073062</v>
+        <v>32.43359593</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1164736598903111</v>
+        <v>0.1170948286637113</v>
       </c>
       <c r="T4">
-        <v>0.9211147077841277</v>
+        <v>0.92921061924652</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>139.9844309998693</v>
+        <v>93.32295399991287</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1148646338038</v>
+        <v>0.1147299809150951</v>
       </c>
       <c r="C5">
-        <v>224.4527828729949</v>
+        <v>222.8613210879339</v>
       </c>
       <c r="D5">
-        <v>228.5867828729949</v>
+        <v>229.0333210879339</v>
       </c>
       <c r="E5">
-        <v>-121.486</v>
+        <v>-119.448</v>
       </c>
       <c r="F5">
-        <v>6.114</v>
+        <v>8.152000000000001</v>
       </c>
       <c r="G5">
         <v>1.98</v>
@@ -1825,28 +1825,28 @@
         <v>28.7</v>
       </c>
       <c r="M5">
-        <v>0.3075342</v>
+        <v>0.4100456</v>
       </c>
       <c r="N5">
-        <v>28.3924658</v>
+        <v>28.2899544</v>
       </c>
       <c r="O5">
-        <v>4.258869870000001</v>
+        <v>4.24349316</v>
       </c>
       <c r="P5">
-        <v>24.13359593</v>
+        <v>24.04646124</v>
       </c>
       <c r="Q5">
-        <v>32.43359593</v>
+        <v>32.34646124</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1170948286637113</v>
+        <v>0.1177289384532241</v>
       </c>
       <c r="T5">
-        <v>0.92921061924652</v>
+        <v>0.9374751955310456</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>93.32295399991287</v>
+        <v>69.99221549993464</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1147299809150951</v>
+        <v>0.1145953280263902</v>
       </c>
       <c r="C6">
-        <v>222.8613210879339</v>
+        <v>221.2716073186839</v>
       </c>
       <c r="D6">
-        <v>229.0333210879339</v>
+        <v>229.481607318684</v>
       </c>
       <c r="E6">
-        <v>-119.448</v>
+        <v>-117.41</v>
       </c>
       <c r="F6">
-        <v>8.152000000000001</v>
+        <v>10.19</v>
       </c>
       <c r="G6">
         <v>1.98</v>
@@ -1907,28 +1907,28 @@
         <v>28.7</v>
       </c>
       <c r="M6">
-        <v>0.4100456</v>
+        <v>0.512557</v>
       </c>
       <c r="N6">
-        <v>28.2899544</v>
+        <v>28.187443</v>
       </c>
       <c r="O6">
-        <v>4.24349316</v>
+        <v>4.22811645</v>
       </c>
       <c r="P6">
-        <v>24.04646124</v>
+        <v>23.95932655</v>
       </c>
       <c r="Q6">
-        <v>32.34646124</v>
+        <v>32.25932655</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1177289384532241</v>
+        <v>0.118376397922516</v>
       </c>
       <c r="T6">
-        <v>0.9374751955310456</v>
+        <v>0.9459137628952455</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>69.99221549993464</v>
+        <v>55.99377239994772</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1145953280263902</v>
+        <v>0.1144606751376854</v>
       </c>
       <c r="C7">
-        <v>221.2716073186839</v>
+        <v>219.6836518495326</v>
       </c>
       <c r="D7">
-        <v>229.481607318684</v>
+        <v>229.9316518495326</v>
       </c>
       <c r="E7">
-        <v>-117.41</v>
+        <v>-115.372</v>
       </c>
       <c r="F7">
-        <v>10.19</v>
+        <v>12.228</v>
       </c>
       <c r="G7">
         <v>1.98</v>
@@ -1989,28 +1989,28 @@
         <v>28.7</v>
       </c>
       <c r="M7">
-        <v>0.512557</v>
+        <v>0.6150684000000001</v>
       </c>
       <c r="N7">
-        <v>28.187443</v>
+        <v>28.0849316</v>
       </c>
       <c r="O7">
-        <v>4.22811645</v>
+        <v>4.212739740000001</v>
       </c>
       <c r="P7">
-        <v>23.95932655</v>
+        <v>23.87219186</v>
       </c>
       <c r="Q7">
-        <v>32.25932655</v>
+        <v>32.17219186000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.118376397922516</v>
+        <v>0.1190376331251972</v>
       </c>
       <c r="T7">
-        <v>0.9459137628952455</v>
+        <v>0.9545318742459176</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>55.99377239994772</v>
+        <v>46.66147699995643</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1144606751376853</v>
+        <v>0.1143260222489805</v>
       </c>
       <c r="C8">
-        <v>219.6836518495327</v>
+        <v>218.0974650456018</v>
       </c>
       <c r="D8">
-        <v>229.9316518495327</v>
+        <v>230.3834650456018</v>
       </c>
       <c r="E8">
-        <v>-115.372</v>
+        <v>-113.334</v>
       </c>
       <c r="F8">
-        <v>12.228</v>
+        <v>14.266</v>
       </c>
       <c r="G8">
         <v>1.98</v>
@@ -2071,28 +2071,28 @@
         <v>28.7</v>
       </c>
       <c r="M8">
-        <v>0.6150684</v>
+        <v>0.7175798</v>
       </c>
       <c r="N8">
-        <v>28.0849316</v>
+        <v>27.9824202</v>
       </c>
       <c r="O8">
-        <v>4.212739740000001</v>
+        <v>4.19736303</v>
       </c>
       <c r="P8">
-        <v>23.87219186</v>
+        <v>23.78505717</v>
       </c>
       <c r="Q8">
-        <v>32.17219186000001</v>
+        <v>32.08505717</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1190376331251972</v>
+        <v>0.119713088439764</v>
       </c>
       <c r="T8">
-        <v>0.9545318742459176</v>
+        <v>0.9633353213245612</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>46.66147699995643</v>
+        <v>39.99555171424837</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1143260222489805</v>
+        <v>0.1141913693602756</v>
       </c>
       <c r="C9">
-        <v>218.0974650456019</v>
+        <v>216.513057353643</v>
       </c>
       <c r="D9">
-        <v>230.3834650456019</v>
+        <v>230.837057353643</v>
       </c>
       <c r="E9">
-        <v>-113.334</v>
+        <v>-111.296</v>
       </c>
       <c r="F9">
-        <v>14.266</v>
+        <v>16.304</v>
       </c>
       <c r="G9">
         <v>1.98</v>
@@ -2153,28 +2153,28 @@
         <v>28.7</v>
       </c>
       <c r="M9">
-        <v>0.7175798000000001</v>
+        <v>0.8200912</v>
       </c>
       <c r="N9">
-        <v>27.9824202</v>
+        <v>27.8799088</v>
       </c>
       <c r="O9">
-        <v>4.19736303</v>
+        <v>4.18198632</v>
       </c>
       <c r="P9">
-        <v>23.78505717</v>
+        <v>23.69792248</v>
       </c>
       <c r="Q9">
-        <v>32.08505717</v>
+        <v>31.99792248</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.119713088439764</v>
+        <v>0.120403227565517</v>
       </c>
       <c r="T9">
-        <v>0.9633353213245612</v>
+        <v>0.9723301476875232</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.99555171424836</v>
+        <v>34.99610774996732</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1141913693602756</v>
+        <v>0.1140567164715707</v>
       </c>
       <c r="C10">
-        <v>216.513057353643</v>
+        <v>214.9304393028428</v>
       </c>
       <c r="D10">
-        <v>230.837057353643</v>
+        <v>231.2924393028429</v>
       </c>
       <c r="E10">
-        <v>-111.296</v>
+        <v>-109.258</v>
       </c>
       <c r="F10">
-        <v>16.304</v>
+        <v>18.342</v>
       </c>
       <c r="G10">
         <v>1.98</v>
@@ -2235,28 +2235,28 @@
         <v>28.7</v>
       </c>
       <c r="M10">
-        <v>0.8200912</v>
+        <v>0.9226025999999999</v>
       </c>
       <c r="N10">
-        <v>27.8799088</v>
+        <v>27.7773974</v>
       </c>
       <c r="O10">
-        <v>4.18198632</v>
+        <v>4.16660961</v>
       </c>
       <c r="P10">
-        <v>23.69792248</v>
+        <v>23.61078779</v>
       </c>
       <c r="Q10">
-        <v>31.99792248</v>
+        <v>31.91078779</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.120403227565517</v>
+        <v>0.1211085345841437</v>
       </c>
       <c r="T10">
-        <v>0.9723301476875232</v>
+        <v>0.9815226625419787</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.99610774996732</v>
+        <v>31.10765133330429</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1140567164715707</v>
+        <v>0.1139220635828659</v>
       </c>
       <c r="C11">
-        <v>214.9304393028428</v>
+        <v>213.3496215056373</v>
       </c>
       <c r="D11">
-        <v>231.2924393028429</v>
+        <v>231.7496215056373</v>
       </c>
       <c r="E11">
-        <v>-109.258</v>
+        <v>-107.22</v>
       </c>
       <c r="F11">
-        <v>18.342</v>
+        <v>20.38</v>
       </c>
       <c r="G11">
         <v>1.98</v>
@@ -2317,28 +2317,28 @@
         <v>28.7</v>
       </c>
       <c r="M11">
-        <v>0.9226025999999999</v>
+        <v>1.025114</v>
       </c>
       <c r="N11">
-        <v>27.7773974</v>
+        <v>27.674886</v>
       </c>
       <c r="O11">
-        <v>4.16660961</v>
+        <v>4.1512329</v>
       </c>
       <c r="P11">
-        <v>23.61078779</v>
+        <v>23.5236531</v>
       </c>
       <c r="Q11">
-        <v>31.91078779</v>
+        <v>31.8236531</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1211085345841437</v>
+        <v>0.1218295150920732</v>
       </c>
       <c r="T11">
-        <v>0.9815226625419787</v>
+        <v>0.9909194555043113</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>31.10765133330429</v>
+        <v>27.99688619997386</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1139220635828659</v>
+        <v>0.113787410694161</v>
       </c>
       <c r="C12">
-        <v>213.3496215056373</v>
+        <v>211.770614658537</v>
       </c>
       <c r="D12">
-        <v>231.7496215056373</v>
+        <v>232.208614658537</v>
       </c>
       <c r="E12">
-        <v>-107.22</v>
+        <v>-105.182</v>
       </c>
       <c r="F12">
-        <v>20.38</v>
+        <v>22.418</v>
       </c>
       <c r="G12">
         <v>1.98</v>
@@ -2399,28 +2399,28 @@
         <v>28.7</v>
       </c>
       <c r="M12">
-        <v>1.025114</v>
+        <v>1.1276254</v>
       </c>
       <c r="N12">
-        <v>27.674886</v>
+        <v>27.5723746</v>
       </c>
       <c r="O12">
-        <v>4.1512329</v>
+        <v>4.13585619</v>
       </c>
       <c r="P12">
-        <v>23.5236531</v>
+        <v>23.43651841000001</v>
       </c>
       <c r="Q12">
-        <v>31.8236531</v>
+        <v>31.73651841</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1218295150920732</v>
+        <v>0.1225666974091697</v>
       </c>
       <c r="T12">
-        <v>0.9909194555043113</v>
+        <v>1.000527412353438</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.99688619997386</v>
+        <v>25.45171472724896</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.113787410694161</v>
+        <v>0.1136527578054561</v>
       </c>
       <c r="C13">
-        <v>211.770614658537</v>
+        <v>210.1934295429604</v>
       </c>
       <c r="D13">
-        <v>232.208614658537</v>
+        <v>232.6694295429604</v>
       </c>
       <c r="E13">
-        <v>-105.182</v>
+        <v>-103.144</v>
       </c>
       <c r="F13">
-        <v>22.418</v>
+        <v>24.456</v>
       </c>
       <c r="G13">
         <v>1.98</v>
@@ -2481,28 +2481,28 @@
         <v>28.7</v>
       </c>
       <c r="M13">
-        <v>1.1276254</v>
+        <v>1.2301368</v>
       </c>
       <c r="N13">
-        <v>27.5723746</v>
+        <v>27.4698632</v>
       </c>
       <c r="O13">
-        <v>4.13585619</v>
+        <v>4.12047948</v>
       </c>
       <c r="P13">
-        <v>23.43651841000001</v>
+        <v>23.34938372</v>
       </c>
       <c r="Q13">
-        <v>31.73651841</v>
+        <v>31.64938372</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1225666974091697</v>
+        <v>0.1233206338698365</v>
       </c>
       <c r="T13">
-        <v>1.000527412353438</v>
+        <v>1.010353731858226</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.45171472724896</v>
+        <v>23.33073849997822</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1136527578054561</v>
+        <v>0.1135181049167513</v>
       </c>
       <c r="C14">
-        <v>210.1934295429604</v>
+        <v>208.6180770260786</v>
       </c>
       <c r="D14">
-        <v>232.6694295429604</v>
+        <v>233.1320770260786</v>
       </c>
       <c r="E14">
-        <v>-103.144</v>
+        <v>-101.106</v>
       </c>
       <c r="F14">
-        <v>24.456</v>
+        <v>26.494</v>
       </c>
       <c r="G14">
         <v>1.98</v>
@@ -2563,28 +2563,28 @@
         <v>28.7</v>
       </c>
       <c r="M14">
-        <v>1.2301368</v>
+        <v>1.3326482</v>
       </c>
       <c r="N14">
-        <v>27.4698632</v>
+        <v>27.3673518</v>
       </c>
       <c r="O14">
-        <v>4.12047948</v>
+        <v>4.10510277</v>
       </c>
       <c r="P14">
-        <v>23.34938372</v>
+        <v>23.26224903</v>
       </c>
       <c r="Q14">
-        <v>31.64938372</v>
+        <v>31.56224903</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1233206338698365</v>
+        <v>0.1240919022031624</v>
       </c>
       <c r="T14">
-        <v>1.010353731858226</v>
+        <v>1.020405943765423</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.33073849997822</v>
+        <v>21.5360663076722</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1135181049167513</v>
+        <v>0.1133834520280464</v>
       </c>
       <c r="C15">
-        <v>208.6180770260786</v>
+        <v>207.0445680616698</v>
       </c>
       <c r="D15">
-        <v>233.1320770260786</v>
+        <v>233.5965680616698</v>
       </c>
       <c r="E15">
-        <v>-101.106</v>
+        <v>-99.06799999999998</v>
       </c>
       <c r="F15">
-        <v>26.494</v>
+        <v>28.532</v>
       </c>
       <c r="G15">
         <v>1.98</v>
@@ -2645,28 +2645,28 @@
         <v>28.7</v>
       </c>
       <c r="M15">
-        <v>1.3326482</v>
+        <v>1.4351596</v>
       </c>
       <c r="N15">
-        <v>27.3673518</v>
+        <v>27.2648404</v>
       </c>
       <c r="O15">
-        <v>4.10510277</v>
+        <v>4.08972606</v>
       </c>
       <c r="P15">
-        <v>23.26224903</v>
+        <v>23.17511434</v>
       </c>
       <c r="Q15">
-        <v>31.56224903</v>
+        <v>31.47511434</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1240919022031624</v>
+        <v>0.1248811070093563</v>
       </c>
       <c r="T15">
-        <v>1.020405943765423</v>
+        <v>1.030691928042555</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.5360663076722</v>
+        <v>19.99777585712418</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1133834520280464</v>
+        <v>0.1132487991393415</v>
       </c>
       <c r="C16">
-        <v>207.0445680616698</v>
+        <v>205.4729136909829</v>
       </c>
       <c r="D16">
-        <v>233.5965680616698</v>
+        <v>234.0629136909829</v>
       </c>
       <c r="E16">
-        <v>-99.06799999999998</v>
+        <v>-97.02999999999999</v>
       </c>
       <c r="F16">
-        <v>28.532</v>
+        <v>30.57000000000001</v>
       </c>
       <c r="G16">
         <v>1.98</v>
@@ -2727,28 +2727,28 @@
         <v>28.7</v>
       </c>
       <c r="M16">
-        <v>1.4351596</v>
+        <v>1.537671</v>
       </c>
       <c r="N16">
-        <v>27.2648404</v>
+        <v>27.162329</v>
       </c>
       <c r="O16">
-        <v>4.08972606</v>
+        <v>4.07434935</v>
       </c>
       <c r="P16">
-        <v>23.17511434</v>
+        <v>23.08797965</v>
       </c>
       <c r="Q16">
-        <v>31.47511434</v>
+        <v>31.38797965</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1248811070093563</v>
+        <v>0.1256888813404018</v>
       </c>
       <c r="T16">
-        <v>1.030691928042555</v>
+        <v>1.041219935479149</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.99777585712418</v>
+        <v>18.66459079998257</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1132487991393415</v>
+        <v>0.1131141462506366</v>
       </c>
       <c r="C17">
-        <v>205.4729136909829</v>
+        <v>203.9031250436132</v>
       </c>
       <c r="D17">
-        <v>234.0629136909829</v>
+        <v>234.5311250436132</v>
       </c>
       <c r="E17">
-        <v>-97.03</v>
+        <v>-94.99199999999999</v>
       </c>
       <c r="F17">
-        <v>30.57</v>
+        <v>32.608</v>
       </c>
       <c r="G17">
         <v>1.98</v>
@@ -2809,28 +2809,28 @@
         <v>28.7</v>
       </c>
       <c r="M17">
-        <v>1.537671</v>
+        <v>1.6401824</v>
       </c>
       <c r="N17">
-        <v>27.162329</v>
+        <v>27.0598176</v>
       </c>
       <c r="O17">
-        <v>4.07434935</v>
+        <v>4.05897264</v>
       </c>
       <c r="P17">
-        <v>23.08797965</v>
+        <v>23.00084496</v>
       </c>
       <c r="Q17">
-        <v>31.38797965</v>
+        <v>31.30084496</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1256888813404018</v>
+        <v>0.1265158883936151</v>
       </c>
       <c r="T17">
-        <v>1.041219935479149</v>
+        <v>1.051998609759472</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.66459079998257</v>
+        <v>17.49805387498366</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1131141462506366</v>
+        <v>0.1129794933619318</v>
       </c>
       <c r="C18">
-        <v>203.9031250436132</v>
+        <v>202.3352133383877</v>
       </c>
       <c r="D18">
-        <v>234.5311250436132</v>
+        <v>235.0012133383877</v>
       </c>
       <c r="E18">
-        <v>-94.99199999999999</v>
+        <v>-92.95399999999998</v>
       </c>
       <c r="F18">
-        <v>32.608</v>
+        <v>34.64600000000001</v>
       </c>
       <c r="G18">
         <v>1.98</v>
@@ -2891,28 +2891,28 @@
         <v>28.7</v>
       </c>
       <c r="M18">
-        <v>1.6401824</v>
+        <v>1.7426938</v>
       </c>
       <c r="N18">
-        <v>27.0598176</v>
+        <v>26.9573062</v>
       </c>
       <c r="O18">
-        <v>4.05897264</v>
+        <v>4.04359593</v>
       </c>
       <c r="P18">
-        <v>23.00084496</v>
+        <v>22.91371027</v>
       </c>
       <c r="Q18">
-        <v>31.30084496</v>
+        <v>31.21371027</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1265158883936151</v>
+        <v>0.1273628233276287</v>
       </c>
       <c r="T18">
-        <v>1.051998609759472</v>
+        <v>1.063037011130886</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.49805387498366</v>
+        <v>16.46875658821991</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1129794933619318</v>
+        <v>0.1128448404732269</v>
       </c>
       <c r="C19">
-        <v>202.3352133383877</v>
+        <v>200.7691898842607</v>
       </c>
       <c r="D19">
-        <v>235.0012133383877</v>
+        <v>235.4731898842607</v>
       </c>
       <c r="E19">
-        <v>-92.95399999999998</v>
+        <v>-90.916</v>
       </c>
       <c r="F19">
-        <v>34.64600000000001</v>
+        <v>36.684</v>
       </c>
       <c r="G19">
         <v>1.98</v>
@@ -2973,28 +2973,28 @@
         <v>28.7</v>
       </c>
       <c r="M19">
-        <v>1.7426938</v>
+        <v>1.8452052</v>
       </c>
       <c r="N19">
-        <v>26.9573062</v>
+        <v>26.8547948</v>
       </c>
       <c r="O19">
-        <v>4.04359593</v>
+        <v>4.02821922</v>
       </c>
       <c r="P19">
-        <v>22.91371027</v>
+        <v>22.82657558</v>
       </c>
       <c r="Q19">
-        <v>31.21371027</v>
+        <v>31.12657558</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1273628233276287</v>
+        <v>0.1282304152112523</v>
       </c>
       <c r="T19">
-        <v>1.063037011130886</v>
+        <v>1.074344641804043</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.46875658821991</v>
+        <v>15.55382566665214</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1128448404732269</v>
+        <v>0.112710187584522</v>
       </c>
       <c r="C20">
-        <v>200.7691898842607</v>
+        <v>199.2050660812213</v>
       </c>
       <c r="D20">
-        <v>235.4731898842607</v>
+        <v>235.9470660812213</v>
       </c>
       <c r="E20">
-        <v>-90.916</v>
+        <v>-88.87799999999999</v>
       </c>
       <c r="F20">
-        <v>36.684</v>
+        <v>38.722</v>
       </c>
       <c r="G20">
         <v>1.98</v>
@@ -3055,28 +3055,28 @@
         <v>28.7</v>
       </c>
       <c r="M20">
-        <v>1.8452052</v>
+        <v>1.9477166</v>
       </c>
       <c r="N20">
-        <v>26.8547948</v>
+        <v>26.7522834</v>
       </c>
       <c r="O20">
-        <v>4.02821922</v>
+        <v>4.01284251</v>
       </c>
       <c r="P20">
-        <v>22.82657558</v>
+        <v>22.73944089</v>
       </c>
       <c r="Q20">
-        <v>31.12657558</v>
+        <v>31.03944089</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1282304152112523</v>
+        <v>0.1291194291166939</v>
       </c>
       <c r="T20">
-        <v>1.074344641804043</v>
+        <v>1.085931473234561</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.55382566665214</v>
+        <v>14.73520326314414</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.112710187584522</v>
+        <v>0.1125755346958172</v>
       </c>
       <c r="C21">
-        <v>199.2050660812213</v>
+        <v>197.6428534212104</v>
       </c>
       <c r="D21">
-        <v>235.9470660812213</v>
+        <v>236.4228534212104</v>
       </c>
       <c r="E21">
-        <v>-88.87799999999999</v>
+        <v>-86.83999999999999</v>
       </c>
       <c r="F21">
-        <v>38.722</v>
+        <v>40.76000000000001</v>
       </c>
       <c r="G21">
         <v>1.98</v>
@@ -3137,28 +3137,28 @@
         <v>28.7</v>
       </c>
       <c r="M21">
-        <v>1.9477166</v>
+        <v>2.050228</v>
       </c>
       <c r="N21">
-        <v>26.7522834</v>
+        <v>26.649772</v>
       </c>
       <c r="O21">
-        <v>4.01284251</v>
+        <v>3.9974658</v>
       </c>
       <c r="P21">
-        <v>22.73944089</v>
+        <v>22.6523062</v>
       </c>
       <c r="Q21">
-        <v>31.03944089</v>
+        <v>30.9523062</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1291194291166939</v>
+        <v>0.1300306683697715</v>
       </c>
       <c r="T21">
-        <v>1.085931473234561</v>
+        <v>1.097807975450842</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.73520326314414</v>
+        <v>13.99844309998693</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1125755346958172</v>
+        <v>0.1124408818071123</v>
       </c>
       <c r="C22">
-        <v>197.6428534212104</v>
+        <v>196.0825634890507</v>
       </c>
       <c r="D22">
-        <v>236.4228534212104</v>
+        <v>236.9005634890507</v>
       </c>
       <c r="E22">
-        <v>-86.83999999999999</v>
+        <v>-84.80199999999999</v>
       </c>
       <c r="F22">
-        <v>40.76000000000001</v>
+        <v>42.79800000000001</v>
       </c>
       <c r="G22">
         <v>1.98</v>
@@ -3219,28 +3219,28 @@
         <v>28.7</v>
       </c>
       <c r="M22">
-        <v>2.050228</v>
+        <v>2.1527394</v>
       </c>
       <c r="N22">
-        <v>26.649772</v>
+        <v>26.5472606</v>
       </c>
       <c r="O22">
-        <v>3.9974658</v>
+        <v>3.98208909</v>
       </c>
       <c r="P22">
-        <v>22.6523062</v>
+        <v>22.56517151</v>
       </c>
       <c r="Q22">
-        <v>30.9523062</v>
+        <v>30.86517151</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1300306683697715</v>
+        <v>0.1309649769710282</v>
       </c>
       <c r="T22">
-        <v>1.097807975450842</v>
+        <v>1.109985148609308</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.99844309998693</v>
+        <v>13.33185057141612</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1124408818071123</v>
+        <v>0.1125867289184074</v>
       </c>
       <c r="C23">
-        <v>196.0825634890507</v>
+        <v>193.5272262364466</v>
       </c>
       <c r="D23">
-        <v>236.9005634890507</v>
+        <v>236.3832262364466</v>
       </c>
       <c r="E23">
-        <v>-84.80199999999999</v>
+        <v>-82.76399999999998</v>
       </c>
       <c r="F23">
-        <v>42.798</v>
+        <v>44.83600000000001</v>
       </c>
       <c r="G23">
         <v>1.98</v>
@@ -3301,45 +3301,45 @@
         <v>28.7</v>
       </c>
       <c r="M23">
-        <v>2.1527394</v>
+        <v>2.3225048</v>
       </c>
       <c r="N23">
-        <v>26.5472606</v>
+        <v>26.3774952</v>
       </c>
       <c r="O23">
-        <v>3.98208909</v>
+        <v>3.95662428</v>
       </c>
       <c r="P23">
-        <v>22.56517151</v>
+        <v>22.42087092</v>
       </c>
       <c r="Q23">
-        <v>30.86517151</v>
+        <v>30.72087092</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1309649769710282</v>
+        <v>0.1319232422030864</v>
       </c>
       <c r="T23">
-        <v>1.109985148609308</v>
+        <v>1.122474556976965</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.15</v>
       </c>
       <c r="W23">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.33185057141612</v>
+        <v>12.35734798050794</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1125867289184074</v>
+        <v>0.1124648260297025</v>
       </c>
       <c r="C24">
-        <v>193.5272262364466</v>
+        <v>191.9214751424404</v>
       </c>
       <c r="D24">
-        <v>236.3832262364466</v>
+        <v>236.8154751424404</v>
       </c>
       <c r="E24">
-        <v>-82.76399999999998</v>
+        <v>-80.726</v>
       </c>
       <c r="F24">
-        <v>44.83600000000001</v>
+        <v>46.874</v>
       </c>
       <c r="G24">
         <v>1.98</v>
@@ -3383,28 +3383,28 @@
         <v>28.7</v>
       </c>
       <c r="M24">
-        <v>2.3225048</v>
+        <v>2.4280732</v>
       </c>
       <c r="N24">
-        <v>26.3774952</v>
+        <v>26.2719268</v>
       </c>
       <c r="O24">
-        <v>3.95662428</v>
+        <v>3.94078902</v>
       </c>
       <c r="P24">
-        <v>22.42087092</v>
+        <v>22.33113778</v>
       </c>
       <c r="Q24">
-        <v>30.72087092</v>
+        <v>30.63113778</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1319232422030864</v>
+        <v>0.1329063974411721</v>
       </c>
       <c r="T24">
-        <v>1.122474556976965</v>
+        <v>1.135288365561963</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.35734798050794</v>
+        <v>11.82007198135542</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1124648260297025</v>
+        <v>0.1123429231409977</v>
       </c>
       <c r="C25">
-        <v>191.9214751424404</v>
+        <v>190.3173077597528</v>
       </c>
       <c r="D25">
-        <v>236.8154751424404</v>
+        <v>237.2493077597528</v>
       </c>
       <c r="E25">
-        <v>-80.726</v>
+        <v>-78.68799999999999</v>
       </c>
       <c r="F25">
-        <v>46.874</v>
+        <v>48.91200000000001</v>
       </c>
       <c r="G25">
         <v>1.98</v>
@@ -3465,28 +3465,28 @@
         <v>28.7</v>
       </c>
       <c r="M25">
-        <v>2.4280732</v>
+        <v>2.5336416</v>
       </c>
       <c r="N25">
-        <v>26.2719268</v>
+        <v>26.1663584</v>
       </c>
       <c r="O25">
-        <v>3.94078902</v>
+        <v>3.92495376</v>
       </c>
       <c r="P25">
-        <v>22.33113778</v>
+        <v>22.24140464</v>
       </c>
       <c r="Q25">
-        <v>30.63113778</v>
+        <v>30.54140464</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1329063974411721</v>
+        <v>0.1339154251855232</v>
       </c>
       <c r="T25">
-        <v>1.135288365561963</v>
+        <v>1.148439379636041</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.82007198135542</v>
+        <v>11.32756898213228</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1123429231409977</v>
+        <v>0.1122210202522928</v>
       </c>
       <c r="C26">
-        <v>190.3173077597528</v>
+        <v>188.714732808168</v>
       </c>
       <c r="D26">
-        <v>237.2493077597528</v>
+        <v>237.684732808168</v>
       </c>
       <c r="E26">
-        <v>-78.68799999999999</v>
+        <v>-76.64999999999999</v>
       </c>
       <c r="F26">
-        <v>48.912</v>
+        <v>50.95</v>
       </c>
       <c r="G26">
         <v>1.98</v>
@@ -3547,28 +3547,28 @@
         <v>28.7</v>
       </c>
       <c r="M26">
-        <v>2.5336416</v>
+        <v>2.63921</v>
       </c>
       <c r="N26">
-        <v>26.1663584</v>
+        <v>26.06079</v>
       </c>
       <c r="O26">
-        <v>3.92495376</v>
+        <v>3.9091185</v>
       </c>
       <c r="P26">
-        <v>22.24140464</v>
+        <v>22.1516715</v>
       </c>
       <c r="Q26">
-        <v>30.54140464</v>
+        <v>30.4516715</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1339154251855232</v>
+        <v>0.1349513603363904</v>
       </c>
       <c r="T26">
-        <v>1.148439379636041</v>
+        <v>1.161941087418761</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.32756898213228</v>
+        <v>10.87446622284699</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1122210202522928</v>
+        <v>0.1120991173635879</v>
       </c>
       <c r="C27">
-        <v>188.714732808168</v>
+        <v>187.1137590716018</v>
       </c>
       <c r="D27">
-        <v>237.684732808168</v>
+        <v>238.1217590716018</v>
       </c>
       <c r="E27">
-        <v>-76.64999999999999</v>
+        <v>-74.61199999999999</v>
       </c>
       <c r="F27">
-        <v>50.95</v>
+        <v>52.98800000000001</v>
       </c>
       <c r="G27">
         <v>1.98</v>
@@ -3629,28 +3629,28 @@
         <v>28.7</v>
       </c>
       <c r="M27">
-        <v>2.63921</v>
+        <v>2.7447784</v>
       </c>
       <c r="N27">
-        <v>26.06079</v>
+        <v>25.9552216</v>
       </c>
       <c r="O27">
-        <v>3.9091185</v>
+        <v>3.89328324</v>
       </c>
       <c r="P27">
-        <v>22.1516715</v>
+        <v>22.06193836</v>
       </c>
       <c r="Q27">
-        <v>30.4516715</v>
+        <v>30.36193836</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1349513603363904</v>
+        <v>0.1360152937345783</v>
       </c>
       <c r="T27">
-        <v>1.161941087418761</v>
+        <v>1.175807706222635</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.87446622284699</v>
+        <v>10.45621752196826</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1120991173635879</v>
+        <v>0.1119772144748831</v>
       </c>
       <c r="C28">
-        <v>187.1137590716018</v>
+        <v>185.5143953986918</v>
       </c>
       <c r="D28">
-        <v>238.1217590716018</v>
+        <v>238.5603953986918</v>
       </c>
       <c r="E28">
-        <v>-74.61199999999999</v>
+        <v>-72.57399999999998</v>
       </c>
       <c r="F28">
-        <v>52.98800000000001</v>
+        <v>55.026</v>
       </c>
       <c r="G28">
         <v>1.98</v>
@@ -3711,28 +3711,28 @@
         <v>28.7</v>
       </c>
       <c r="M28">
-        <v>2.7447784</v>
+        <v>2.8503468</v>
       </c>
       <c r="N28">
-        <v>25.9552216</v>
+        <v>25.8496532</v>
       </c>
       <c r="O28">
-        <v>3.89328324</v>
+        <v>3.87744798</v>
       </c>
       <c r="P28">
-        <v>22.06193836</v>
+        <v>21.97220522</v>
       </c>
       <c r="Q28">
-        <v>30.36193836</v>
+        <v>30.27220522</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1360152937345783</v>
+        <v>0.1371083759929905</v>
       </c>
       <c r="T28">
-        <v>1.175807706222635</v>
+        <v>1.190054232390999</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.45621752196826</v>
+        <v>10.0689502063398</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1119772144748831</v>
+        <v>0.1122599115861782</v>
       </c>
       <c r="C29">
-        <v>185.5143953986918</v>
+        <v>182.4616433016899</v>
       </c>
       <c r="D29">
-        <v>238.5603953986918</v>
+        <v>237.54564330169</v>
       </c>
       <c r="E29">
-        <v>-72.57399999999998</v>
+        <v>-70.53599999999999</v>
       </c>
       <c r="F29">
-        <v>55.026</v>
+        <v>57.06400000000001</v>
       </c>
       <c r="G29">
         <v>1.98</v>
@@ -3793,45 +3793,45 @@
         <v>28.7</v>
       </c>
       <c r="M29">
-        <v>2.8503468</v>
+        <v>3.052924</v>
       </c>
       <c r="N29">
-        <v>25.8496532</v>
+        <v>25.647076</v>
       </c>
       <c r="O29">
-        <v>3.87744798</v>
+        <v>3.8470614</v>
       </c>
       <c r="P29">
-        <v>21.97220522</v>
+        <v>21.8000146</v>
       </c>
       <c r="Q29">
-        <v>30.27220522</v>
+        <v>30.1000146</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1371083759929905</v>
+        <v>0.1382318216474697</v>
       </c>
       <c r="T29">
-        <v>1.190054232390999</v>
+        <v>1.204696495397373</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.15</v>
       </c>
       <c r="W29">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>10.0689502063398</v>
+        <v>9.400823603863049</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1122599115861782</v>
+        <v>0.1121524586974733</v>
       </c>
       <c r="C30">
-        <v>182.4616433016899</v>
+        <v>180.8083308637349</v>
       </c>
       <c r="D30">
-        <v>237.54564330169</v>
+        <v>237.930330863735</v>
       </c>
       <c r="E30">
-        <v>-70.53599999999999</v>
+        <v>-68.49799999999999</v>
       </c>
       <c r="F30">
-        <v>57.06400000000001</v>
+        <v>59.10200000000001</v>
       </c>
       <c r="G30">
         <v>1.98</v>
@@ -3875,28 +3875,28 @@
         <v>28.7</v>
       </c>
       <c r="M30">
-        <v>3.052924</v>
+        <v>3.161957000000001</v>
       </c>
       <c r="N30">
-        <v>25.647076</v>
+        <v>25.538043</v>
       </c>
       <c r="O30">
-        <v>3.8470614</v>
+        <v>3.83070645</v>
       </c>
       <c r="P30">
-        <v>21.8000146</v>
+        <v>21.70733655</v>
       </c>
       <c r="Q30">
-        <v>30.1000146</v>
+        <v>30.00733655</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1382318216474697</v>
+        <v>0.1393869136584131</v>
       </c>
       <c r="T30">
-        <v>1.204696495397373</v>
+        <v>1.219751216516603</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.400823603863049</v>
+        <v>9.076657272695359</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1121524586974733</v>
+        <v>0.1120450058087684</v>
       </c>
       <c r="C31">
-        <v>180.8083308637349</v>
+        <v>179.1562663927561</v>
       </c>
       <c r="D31">
-        <v>237.930330863735</v>
+        <v>238.3162663927561</v>
       </c>
       <c r="E31">
-        <v>-68.49799999999999</v>
+        <v>-66.45999999999999</v>
       </c>
       <c r="F31">
-        <v>59.102</v>
+        <v>61.14</v>
       </c>
       <c r="G31">
         <v>1.98</v>
@@ -3957,28 +3957,28 @@
         <v>28.7</v>
       </c>
       <c r="M31">
-        <v>3.161957</v>
+        <v>3.27099</v>
       </c>
       <c r="N31">
-        <v>25.538043</v>
+        <v>25.42901</v>
       </c>
       <c r="O31">
-        <v>3.83070645</v>
+        <v>3.8143515</v>
       </c>
       <c r="P31">
-        <v>21.70733655</v>
+        <v>21.6146585</v>
       </c>
       <c r="Q31">
-        <v>30.00733655</v>
+        <v>29.9146585</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1393869136584131</v>
+        <v>0.1405750082982406</v>
       </c>
       <c r="T31">
-        <v>1.219751216516603</v>
+        <v>1.235236072524954</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.07665727269536</v>
+        <v>8.774102030272182</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1120450058087684</v>
+        <v>0.1119375529200636</v>
       </c>
       <c r="C32">
-        <v>179.1562663927561</v>
+        <v>177.5054559714242</v>
       </c>
       <c r="D32">
-        <v>238.3162663927561</v>
+        <v>238.7034559714242</v>
       </c>
       <c r="E32">
-        <v>-66.45999999999999</v>
+        <v>-64.422</v>
       </c>
       <c r="F32">
-        <v>61.14</v>
+        <v>63.178</v>
       </c>
       <c r="G32">
         <v>1.98</v>
@@ -4039,28 +4039,28 @@
         <v>28.7</v>
       </c>
       <c r="M32">
-        <v>3.27099</v>
+        <v>3.380023</v>
       </c>
       <c r="N32">
-        <v>25.42901</v>
+        <v>25.319977</v>
       </c>
       <c r="O32">
-        <v>3.8143515</v>
+        <v>3.79799655</v>
       </c>
       <c r="P32">
-        <v>21.6146585</v>
+        <v>21.52198045</v>
       </c>
       <c r="Q32">
-        <v>29.9146585</v>
+        <v>29.82198045</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1405750082982406</v>
+        <v>0.1417975404638603</v>
       </c>
       <c r="T32">
-        <v>1.235236072524954</v>
+        <v>1.251169764939343</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.774102030272182</v>
+        <v>8.491066480908563</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1119375529200636</v>
+        <v>0.1118301000313587</v>
       </c>
       <c r="C33">
-        <v>177.5054559714242</v>
+        <v>175.8559057220044</v>
       </c>
       <c r="D33">
-        <v>238.7034559714242</v>
+        <v>239.0919057220044</v>
       </c>
       <c r="E33">
-        <v>-64.422</v>
+        <v>-62.38399999999999</v>
       </c>
       <c r="F33">
-        <v>63.178</v>
+        <v>65.21600000000001</v>
       </c>
       <c r="G33">
         <v>1.98</v>
@@ -4121,28 +4121,28 @@
         <v>28.7</v>
       </c>
       <c r="M33">
-        <v>3.380023</v>
+        <v>3.489056</v>
       </c>
       <c r="N33">
-        <v>25.319977</v>
+        <v>25.210944</v>
       </c>
       <c r="O33">
-        <v>3.79799655</v>
+        <v>3.7816416</v>
       </c>
       <c r="P33">
-        <v>21.52198045</v>
+        <v>21.4293024</v>
       </c>
       <c r="Q33">
-        <v>29.82198045</v>
+        <v>29.7293024</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1417975404638603</v>
+        <v>0.1430560294578804</v>
       </c>
       <c r="T33">
-        <v>1.251169764939343</v>
+        <v>1.267572095365921</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.491066480908563</v>
+        <v>8.225720653380169</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1118301000313587</v>
+        <v>0.1117226471426538</v>
       </c>
       <c r="C34">
-        <v>175.8559057220044</v>
+        <v>174.2076218066785</v>
       </c>
       <c r="D34">
-        <v>239.0919057220044</v>
+        <v>239.4816218066785</v>
       </c>
       <c r="E34">
-        <v>-62.38399999999999</v>
+        <v>-60.34599999999999</v>
       </c>
       <c r="F34">
-        <v>65.21600000000001</v>
+        <v>67.254</v>
       </c>
       <c r="G34">
         <v>1.98</v>
@@ -4203,28 +4203,28 @@
         <v>28.7</v>
       </c>
       <c r="M34">
-        <v>3.489056</v>
+        <v>3.598089</v>
       </c>
       <c r="N34">
-        <v>25.210944</v>
+        <v>25.101911</v>
       </c>
       <c r="O34">
-        <v>3.7816416</v>
+        <v>3.76528665</v>
       </c>
       <c r="P34">
-        <v>21.4293024</v>
+        <v>21.33662435</v>
       </c>
       <c r="Q34">
-        <v>29.7293024</v>
+        <v>29.63662435</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1430560294578804</v>
+        <v>0.144352085287543</v>
       </c>
       <c r="T34">
-        <v>1.267572095365921</v>
+        <v>1.284464047596277</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.225720653380169</v>
+        <v>7.976456391156527</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1117226471426538</v>
+        <v>0.111615194253949</v>
       </c>
       <c r="C35">
-        <v>174.2076218066785</v>
+        <v>172.5606104278706</v>
       </c>
       <c r="D35">
-        <v>239.4816218066785</v>
+        <v>239.8726104278707</v>
       </c>
       <c r="E35">
-        <v>-60.34599999999999</v>
+        <v>-58.30799999999998</v>
       </c>
       <c r="F35">
-        <v>67.254</v>
+        <v>69.29200000000002</v>
       </c>
       <c r="G35">
         <v>1.98</v>
@@ -4285,28 +4285,28 @@
         <v>28.7</v>
       </c>
       <c r="M35">
-        <v>3.598089</v>
+        <v>3.707122000000001</v>
       </c>
       <c r="N35">
-        <v>25.101911</v>
+        <v>24.992878</v>
       </c>
       <c r="O35">
-        <v>3.76528665</v>
+        <v>3.7489317</v>
       </c>
       <c r="P35">
-        <v>21.33662435</v>
+        <v>21.2439463</v>
       </c>
       <c r="Q35">
-        <v>29.63662435</v>
+        <v>29.5439463</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.144352085287543</v>
+        <v>0.1456874155362863</v>
       </c>
       <c r="T35">
-        <v>1.284464047596277</v>
+        <v>1.301867877166947</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.976456391156527</v>
+        <v>7.741854732593099</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.111615194253949</v>
+        <v>0.1117457413652441</v>
       </c>
       <c r="C36">
-        <v>172.5606104278706</v>
+        <v>170.047755255696</v>
       </c>
       <c r="D36">
-        <v>239.8726104278707</v>
+        <v>239.397755255696</v>
       </c>
       <c r="E36">
-        <v>-58.30799999999998</v>
+        <v>-56.26999999999998</v>
       </c>
       <c r="F36">
-        <v>69.29200000000002</v>
+        <v>71.33000000000001</v>
       </c>
       <c r="G36">
         <v>1.98</v>
@@ -4367,45 +4367,45 @@
         <v>28.7</v>
       </c>
       <c r="M36">
-        <v>3.707122000000001</v>
+        <v>3.873219000000001</v>
       </c>
       <c r="N36">
-        <v>24.992878</v>
+        <v>24.826781</v>
       </c>
       <c r="O36">
-        <v>3.7489317</v>
+        <v>3.72401715</v>
       </c>
       <c r="P36">
-        <v>21.2439463</v>
+        <v>21.10276385</v>
       </c>
       <c r="Q36">
-        <v>29.5439463</v>
+        <v>29.40276385</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1456874155362863</v>
+        <v>0.1470638328696063</v>
       </c>
       <c r="T36">
-        <v>1.301867877166947</v>
+        <v>1.319807209185945</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.15</v>
       </c>
       <c r="W36">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.741854732593099</v>
+        <v>7.409857278919679</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1117457413652441</v>
+        <v>0.1116450884765392</v>
       </c>
       <c r="C37">
-        <v>170.047755255696</v>
+        <v>168.3757062502722</v>
       </c>
       <c r="D37">
-        <v>239.397755255696</v>
+        <v>239.7637062502722</v>
       </c>
       <c r="E37">
-        <v>-56.26999999999998</v>
+        <v>-54.23199999999999</v>
       </c>
       <c r="F37">
-        <v>71.33000000000001</v>
+        <v>73.36800000000001</v>
       </c>
       <c r="G37">
         <v>1.98</v>
@@ -4449,28 +4449,28 @@
         <v>28.7</v>
       </c>
       <c r="M37">
-        <v>3.873219000000001</v>
+        <v>3.983882400000001</v>
       </c>
       <c r="N37">
-        <v>24.826781</v>
+        <v>24.7161176</v>
       </c>
       <c r="O37">
-        <v>3.72401715</v>
+        <v>3.707417640000001</v>
       </c>
       <c r="P37">
-        <v>21.10276385</v>
+        <v>21.00869996</v>
       </c>
       <c r="Q37">
-        <v>29.40276385</v>
+        <v>29.30869996000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1470638328696063</v>
+        <v>0.1484832632445925</v>
       </c>
       <c r="T37">
-        <v>1.319807209185945</v>
+        <v>1.338307145330537</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.409857278919679</v>
+        <v>7.204027910060799</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1116450884765392</v>
+        <v>0.1115444355878343</v>
       </c>
       <c r="C38">
-        <v>168.3757062502722</v>
+        <v>166.7047777662857</v>
       </c>
       <c r="D38">
-        <v>239.7637062502722</v>
+        <v>240.1307777662857</v>
       </c>
       <c r="E38">
-        <v>-54.232</v>
+        <v>-52.19399999999999</v>
       </c>
       <c r="F38">
-        <v>73.36799999999999</v>
+        <v>75.40600000000001</v>
       </c>
       <c r="G38">
         <v>1.98</v>
@@ -4531,28 +4531,28 @@
         <v>28.7</v>
       </c>
       <c r="M38">
-        <v>3.9838824</v>
+        <v>4.094545800000001</v>
       </c>
       <c r="N38">
-        <v>24.7161176</v>
+        <v>24.6054542</v>
       </c>
       <c r="O38">
-        <v>3.707417640000001</v>
+        <v>3.69081813</v>
       </c>
       <c r="P38">
-        <v>21.00869996</v>
+        <v>20.91463607</v>
       </c>
       <c r="Q38">
-        <v>29.30869996000001</v>
+        <v>29.21463607</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1484832632445925</v>
+        <v>0.1499477549013243</v>
       </c>
       <c r="T38">
-        <v>1.338307145330537</v>
+        <v>1.357394381035275</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.2040279100608</v>
+        <v>7.009324453032129</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1115444355878343</v>
+        <v>0.1114437826991295</v>
       </c>
       <c r="C39">
-        <v>166.7047777662857</v>
+        <v>165.0349749580884</v>
       </c>
       <c r="D39">
-        <v>240.1307777662857</v>
+        <v>240.4989749580884</v>
       </c>
       <c r="E39">
-        <v>-52.19399999999999</v>
+        <v>-50.15599999999999</v>
       </c>
       <c r="F39">
-        <v>75.40600000000001</v>
+        <v>77.444</v>
       </c>
       <c r="G39">
         <v>1.98</v>
@@ -4613,28 +4613,28 @@
         <v>28.7</v>
       </c>
       <c r="M39">
-        <v>4.094545800000001</v>
+        <v>4.205209200000001</v>
       </c>
       <c r="N39">
-        <v>24.6054542</v>
+        <v>24.4947908</v>
       </c>
       <c r="O39">
-        <v>3.69081813</v>
+        <v>3.67421862</v>
       </c>
       <c r="P39">
-        <v>20.91463607</v>
+        <v>20.82057218</v>
       </c>
       <c r="Q39">
-        <v>29.21463607</v>
+        <v>29.12057218</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1499477549013243</v>
+        <v>0.1514594882244024</v>
       </c>
       <c r="T39">
-        <v>1.357394381035275</v>
+        <v>1.37709733402081</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.009324453032129</v>
+        <v>6.824868546373389</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1114437826991295</v>
+        <v>0.1113431298104246</v>
       </c>
       <c r="C40">
-        <v>165.0349749580884</v>
+        <v>163.3663030116938</v>
       </c>
       <c r="D40">
-        <v>240.4989749580884</v>
+        <v>240.8683030116939</v>
       </c>
       <c r="E40">
-        <v>-50.15599999999999</v>
+        <v>-48.11799999999998</v>
       </c>
       <c r="F40">
-        <v>77.444</v>
+        <v>79.48200000000001</v>
       </c>
       <c r="G40">
         <v>1.98</v>
@@ -4695,28 +4695,28 @@
         <v>28.7</v>
       </c>
       <c r="M40">
-        <v>4.205209200000001</v>
+        <v>4.315872600000001</v>
       </c>
       <c r="N40">
-        <v>24.4947908</v>
+        <v>24.3841274</v>
       </c>
       <c r="O40">
-        <v>3.67421862</v>
+        <v>3.657619110000001</v>
       </c>
       <c r="P40">
-        <v>20.82057218</v>
+        <v>20.72650829000001</v>
       </c>
       <c r="Q40">
-        <v>29.12057218</v>
+        <v>29.02650829</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1514594882244024</v>
+        <v>0.1530207865744665</v>
       </c>
       <c r="T40">
-        <v>1.37709733402081</v>
+        <v>1.397446285464888</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.824868546373389</v>
+        <v>6.649871916979199</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1113431298104246</v>
+        <v>0.1112424769217197</v>
       </c>
       <c r="C41">
-        <v>163.3663030116938</v>
+        <v>161.6987671450205</v>
       </c>
       <c r="D41">
-        <v>240.8683030116939</v>
+        <v>241.2387671450205</v>
       </c>
       <c r="E41">
-        <v>-48.11799999999998</v>
+        <v>-46.07999999999998</v>
       </c>
       <c r="F41">
-        <v>79.48200000000001</v>
+        <v>81.52000000000001</v>
       </c>
       <c r="G41">
         <v>1.98</v>
@@ -4777,28 +4777,28 @@
         <v>28.7</v>
       </c>
       <c r="M41">
-        <v>4.315872600000001</v>
+        <v>4.426536</v>
       </c>
       <c r="N41">
-        <v>24.3841274</v>
+        <v>24.273464</v>
       </c>
       <c r="O41">
-        <v>3.657619110000001</v>
+        <v>3.6410196</v>
       </c>
       <c r="P41">
-        <v>20.72650829000001</v>
+        <v>20.6324444</v>
       </c>
       <c r="Q41">
-        <v>29.02650829</v>
+        <v>28.9324444</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1530207865744665</v>
+        <v>0.1546341282028662</v>
       </c>
       <c r="T41">
-        <v>1.397446285464888</v>
+        <v>1.418473535290436</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.649871916979199</v>
+        <v>6.48362511905472</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1112424769217197</v>
+        <v>0.1111418240330148</v>
       </c>
       <c r="C42">
-        <v>161.6987671450205</v>
+        <v>160.0323726081384</v>
       </c>
       <c r="D42">
-        <v>241.2387671450205</v>
+        <v>241.6103726081384</v>
       </c>
       <c r="E42">
-        <v>-46.07999999999998</v>
+        <v>-44.04199999999999</v>
       </c>
       <c r="F42">
-        <v>81.52000000000001</v>
+        <v>83.55800000000001</v>
       </c>
       <c r="G42">
         <v>1.98</v>
@@ -4859,28 +4859,28 @@
         <v>28.7</v>
       </c>
       <c r="M42">
-        <v>4.426536</v>
+        <v>4.5371994</v>
       </c>
       <c r="N42">
-        <v>24.273464</v>
+        <v>24.1628006</v>
       </c>
       <c r="O42">
-        <v>3.6410196</v>
+        <v>3.624420090000001</v>
       </c>
       <c r="P42">
-        <v>20.6324444</v>
+        <v>20.53838051</v>
       </c>
       <c r="Q42">
-        <v>28.9324444</v>
+        <v>28.83838051</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1546341282028662</v>
+        <v>0.1563021593779913</v>
       </c>
       <c r="T42">
-        <v>1.418473535290436</v>
+        <v>1.440213573245662</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.48362511905472</v>
+        <v>6.325487921028994</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1111418240330148</v>
+        <v>0.11104117114431</v>
       </c>
       <c r="C43">
-        <v>160.0323726081384</v>
+        <v>158.3671246835154</v>
       </c>
       <c r="D43">
-        <v>241.6103726081384</v>
+        <v>241.9831246835155</v>
       </c>
       <c r="E43">
-        <v>-44.04199999999999</v>
+        <v>-42.00399999999998</v>
       </c>
       <c r="F43">
-        <v>83.55800000000001</v>
+        <v>85.59600000000002</v>
       </c>
       <c r="G43">
         <v>1.98</v>
@@ -4941,28 +4941,28 @@
         <v>28.7</v>
       </c>
       <c r="M43">
-        <v>4.5371994</v>
+        <v>4.647862800000001</v>
       </c>
       <c r="N43">
-        <v>24.1628006</v>
+        <v>24.0521372</v>
       </c>
       <c r="O43">
-        <v>3.624420090000001</v>
+        <v>3.60782058</v>
       </c>
       <c r="P43">
-        <v>20.53838051</v>
+        <v>20.44431662</v>
       </c>
       <c r="Q43">
-        <v>28.83838051</v>
+        <v>28.74431662</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1563021593779913</v>
+        <v>0.1580277088695</v>
       </c>
       <c r="T43">
-        <v>1.440213573245662</v>
+        <v>1.462703267682103</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.325487921028994</v>
+        <v>6.174881065766398</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.11104117114431</v>
+        <v>0.1113060182556051</v>
       </c>
       <c r="C44">
-        <v>158.3671246835154</v>
+        <v>155.3507637136191</v>
       </c>
       <c r="D44">
-        <v>241.9831246835154</v>
+        <v>241.0047637136191</v>
       </c>
       <c r="E44">
-        <v>-42.00399999999999</v>
+        <v>-39.96599999999999</v>
       </c>
       <c r="F44">
-        <v>85.596</v>
+        <v>87.634</v>
       </c>
       <c r="G44">
         <v>1.98</v>
@@ -5023,45 +5023,45 @@
         <v>28.7</v>
       </c>
       <c r="M44">
-        <v>4.6478628</v>
+        <v>4.8461602</v>
       </c>
       <c r="N44">
-        <v>24.0521372</v>
+        <v>23.8538398</v>
       </c>
       <c r="O44">
-        <v>3.60782058</v>
+        <v>3.57807597</v>
       </c>
       <c r="P44">
-        <v>20.44431662</v>
+        <v>20.27576383</v>
       </c>
       <c r="Q44">
-        <v>28.74431662</v>
+        <v>28.57576383</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1580277088695</v>
+        <v>0.1598138039572019</v>
       </c>
       <c r="T44">
-        <v>1.462703267682103</v>
+        <v>1.485982074204034</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.15</v>
       </c>
       <c r="W44">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.1748810657664</v>
+        <v>5.922214457541045</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1113060182556051</v>
+        <v>0.1112138653669002</v>
       </c>
       <c r="C45">
-        <v>155.3507637136191</v>
+        <v>153.6522832488625</v>
       </c>
       <c r="D45">
-        <v>241.0047637136191</v>
+        <v>241.3442832488626</v>
       </c>
       <c r="E45">
-        <v>-39.96599999999999</v>
+        <v>-37.92799999999998</v>
       </c>
       <c r="F45">
-        <v>87.634</v>
+        <v>89.67200000000001</v>
       </c>
       <c r="G45">
         <v>1.98</v>
@@ -5105,28 +5105,28 @@
         <v>28.7</v>
       </c>
       <c r="M45">
-        <v>4.8461602</v>
+        <v>4.958861600000001</v>
       </c>
       <c r="N45">
-        <v>23.8538398</v>
+        <v>23.7411384</v>
       </c>
       <c r="O45">
-        <v>3.57807597</v>
+        <v>3.56117076</v>
       </c>
       <c r="P45">
-        <v>20.27576383</v>
+        <v>20.17996764</v>
       </c>
       <c r="Q45">
-        <v>28.57576383</v>
+        <v>28.47996764000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1598138039572019</v>
+        <v>0.161663688155179</v>
       </c>
       <c r="T45">
-        <v>1.485982074204034</v>
+        <v>1.510092266673176</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.922214457541045</v>
+        <v>5.787618674415112</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1112138653669002</v>
+        <v>0.1111217124781954</v>
       </c>
       <c r="C46">
-        <v>153.6522832488625</v>
+        <v>151.9547607414148</v>
       </c>
       <c r="D46">
-        <v>241.3442832488626</v>
+        <v>241.6847607414148</v>
       </c>
       <c r="E46">
-        <v>-37.92799999999998</v>
+        <v>-35.88999999999999</v>
       </c>
       <c r="F46">
-        <v>89.67200000000001</v>
+        <v>91.71000000000001</v>
       </c>
       <c r="G46">
         <v>1.98</v>
@@ -5187,28 +5187,28 @@
         <v>28.7</v>
       </c>
       <c r="M46">
-        <v>4.958861600000001</v>
+        <v>5.071563</v>
       </c>
       <c r="N46">
-        <v>23.7411384</v>
+        <v>23.628437</v>
       </c>
       <c r="O46">
-        <v>3.56117076</v>
+        <v>3.54426555</v>
       </c>
       <c r="P46">
-        <v>20.17996764</v>
+        <v>20.08417145</v>
       </c>
       <c r="Q46">
-        <v>28.47996764000001</v>
+        <v>28.38417145</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.161663688155179</v>
+        <v>0.1635808408694461</v>
       </c>
       <c r="T46">
-        <v>1.510092266673176</v>
+        <v>1.535079193413924</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.787618674415112</v>
+        <v>5.659004926094776</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1111217124781954</v>
+        <v>0.1110295595894905</v>
       </c>
       <c r="C47">
-        <v>151.9547607414148</v>
+        <v>150.2582002513306</v>
       </c>
       <c r="D47">
-        <v>241.6847607414148</v>
+        <v>242.0262002513306</v>
       </c>
       <c r="E47">
-        <v>-35.88999999999999</v>
+        <v>-33.85199999999999</v>
       </c>
       <c r="F47">
-        <v>91.71000000000001</v>
+        <v>93.748</v>
       </c>
       <c r="G47">
         <v>1.98</v>
@@ -5269,28 +5269,28 @@
         <v>28.7</v>
       </c>
       <c r="M47">
-        <v>5.071563</v>
+        <v>5.1842644</v>
       </c>
       <c r="N47">
-        <v>23.628437</v>
+        <v>23.5157356</v>
       </c>
       <c r="O47">
-        <v>3.54426555</v>
+        <v>3.52736034</v>
       </c>
       <c r="P47">
-        <v>20.08417145</v>
+        <v>19.98837526</v>
       </c>
       <c r="Q47">
-        <v>28.38417145</v>
+        <v>28.28837526</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1635808408694461</v>
+        <v>0.1655689992397972</v>
       </c>
       <c r="T47">
-        <v>1.535079193413924</v>
+        <v>1.56099156188581</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.659004926094776</v>
+        <v>5.535983079875325</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1110295595894905</v>
+        <v>0.1109374067007856</v>
       </c>
       <c r="C48">
-        <v>150.2582002513306</v>
+        <v>148.562605861641</v>
       </c>
       <c r="D48">
-        <v>242.0262002513306</v>
+        <v>242.3686058616411</v>
       </c>
       <c r="E48">
-        <v>-33.85199999999999</v>
+        <v>-31.81399999999998</v>
       </c>
       <c r="F48">
-        <v>93.748</v>
+        <v>95.78600000000002</v>
       </c>
       <c r="G48">
         <v>1.98</v>
@@ -5351,28 +5351,28 @@
         <v>28.7</v>
       </c>
       <c r="M48">
-        <v>5.1842644</v>
+        <v>5.296965800000001</v>
       </c>
       <c r="N48">
-        <v>23.5157356</v>
+        <v>23.4030342</v>
       </c>
       <c r="O48">
-        <v>3.52736034</v>
+        <v>3.51045513</v>
       </c>
       <c r="P48">
-        <v>19.98837526</v>
+        <v>19.89257907</v>
       </c>
       <c r="Q48">
-        <v>28.28837526</v>
+        <v>28.19257907</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1655689992397972</v>
+        <v>0.1676321824543125</v>
       </c>
       <c r="T48">
-        <v>1.56099156188581</v>
+        <v>1.587881755583051</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.535983079875325</v>
+        <v>5.418196205835423</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1109374067007856</v>
+        <v>0.1108452538120807</v>
       </c>
       <c r="C49">
-        <v>148.562605861641</v>
+        <v>146.8679816785155</v>
       </c>
       <c r="D49">
-        <v>242.3686058616411</v>
+        <v>242.7119816785155</v>
       </c>
       <c r="E49">
-        <v>-31.81399999999998</v>
+        <v>-29.77599999999998</v>
       </c>
       <c r="F49">
-        <v>95.78600000000002</v>
+        <v>97.82400000000001</v>
       </c>
       <c r="G49">
         <v>1.98</v>
@@ -5433,28 +5433,28 @@
         <v>28.7</v>
       </c>
       <c r="M49">
-        <v>5.296965800000001</v>
+        <v>5.409667200000001</v>
       </c>
       <c r="N49">
-        <v>23.4030342</v>
+        <v>23.2903328</v>
       </c>
       <c r="O49">
-        <v>3.51045513</v>
+        <v>3.49354992</v>
       </c>
       <c r="P49">
-        <v>19.89257907</v>
+        <v>19.79678288</v>
       </c>
       <c r="Q49">
-        <v>28.19257907</v>
+        <v>28.09678288</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1676321824543125</v>
+        <v>0.1697747188693861</v>
       </c>
       <c r="T49">
-        <v>1.587881755583051</v>
+        <v>1.615806187499416</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.418196205835423</v>
+        <v>5.305317118213852</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1108452538120807</v>
+        <v>0.1107531009233759</v>
       </c>
       <c r="C50">
-        <v>146.8679816785155</v>
+        <v>145.1743318314257</v>
       </c>
       <c r="D50">
-        <v>242.7119816785155</v>
+        <v>243.0563318314257</v>
       </c>
       <c r="E50">
-        <v>-29.776</v>
+        <v>-27.73799999999999</v>
       </c>
       <c r="F50">
-        <v>97.824</v>
+        <v>99.86200000000001</v>
       </c>
       <c r="G50">
         <v>1.98</v>
@@ -5515,28 +5515,28 @@
         <v>28.7</v>
       </c>
       <c r="M50">
-        <v>5.4096672</v>
+        <v>5.522368600000001</v>
       </c>
       <c r="N50">
-        <v>23.2903328</v>
+        <v>23.1776314</v>
       </c>
       <c r="O50">
-        <v>3.49354992</v>
+        <v>3.47664471</v>
       </c>
       <c r="P50">
-        <v>19.79678288</v>
+        <v>19.70098669</v>
       </c>
       <c r="Q50">
-        <v>28.09678288</v>
+        <v>28.00098669</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1697747188693861</v>
+        <v>0.1720012763203448</v>
       </c>
       <c r="T50">
-        <v>1.615806187499416</v>
+        <v>1.644825695177207</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.305317118213853</v>
+        <v>5.197045340291121</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1107531009233759</v>
+        <v>0.110660948034671</v>
       </c>
       <c r="C51">
-        <v>145.1743318314257</v>
+        <v>143.4816604733121</v>
       </c>
       <c r="D51">
-        <v>243.0563318314257</v>
+        <v>243.4016604733121</v>
       </c>
       <c r="E51">
-        <v>-27.73799999999999</v>
+        <v>-25.69999999999999</v>
       </c>
       <c r="F51">
-        <v>99.86200000000001</v>
+        <v>101.9</v>
       </c>
       <c r="G51">
         <v>1.98</v>
@@ -5597,28 +5597,28 @@
         <v>28.7</v>
       </c>
       <c r="M51">
-        <v>5.522368600000001</v>
+        <v>5.635070000000001</v>
       </c>
       <c r="N51">
-        <v>23.1776314</v>
+        <v>23.06493</v>
       </c>
       <c r="O51">
-        <v>3.47664471</v>
+        <v>3.4597395</v>
       </c>
       <c r="P51">
-        <v>19.70098669</v>
+        <v>19.6051905</v>
       </c>
       <c r="Q51">
-        <v>28.00098669</v>
+        <v>27.9051905</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1720012763203448</v>
+        <v>0.174316896069342</v>
       </c>
       <c r="T51">
-        <v>1.644825695177207</v>
+        <v>1.67500598316211</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.197045340291121</v>
+        <v>5.093104433485299</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.110660948034671</v>
+        <v>0.1105687951459661</v>
       </c>
       <c r="C52">
-        <v>143.4816604733121</v>
+        <v>141.78997178075</v>
       </c>
       <c r="D52">
-        <v>243.4016604733121</v>
+        <v>243.74797178075</v>
       </c>
       <c r="E52">
-        <v>-25.69999999999999</v>
+        <v>-23.66199999999999</v>
       </c>
       <c r="F52">
-        <v>101.9</v>
+        <v>103.938</v>
       </c>
       <c r="G52">
         <v>1.98</v>
@@ -5679,28 +5679,28 @@
         <v>28.7</v>
       </c>
       <c r="M52">
-        <v>5.635070000000001</v>
+        <v>5.7477714</v>
       </c>
       <c r="N52">
-        <v>23.06493</v>
+        <v>22.9522286</v>
       </c>
       <c r="O52">
-        <v>3.4597395</v>
+        <v>3.44283429</v>
       </c>
       <c r="P52">
-        <v>19.6051905</v>
+        <v>19.50939431</v>
       </c>
       <c r="Q52">
-        <v>27.9051905</v>
+        <v>27.80939431</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.174316896069342</v>
+        <v>0.176727030910135</v>
       </c>
       <c r="T52">
-        <v>1.67500598316211</v>
+        <v>1.706418119636192</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.093104433485299</v>
+        <v>4.993239640671861</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1105687951459661</v>
+        <v>0.1104766422572613</v>
       </c>
       <c r="C53">
-        <v>141.78997178075</v>
+        <v>140.0992699541184</v>
       </c>
       <c r="D53">
-        <v>243.74797178075</v>
+        <v>244.0952699541185</v>
       </c>
       <c r="E53">
-        <v>-23.66199999999999</v>
+        <v>-21.62399999999998</v>
       </c>
       <c r="F53">
-        <v>103.938</v>
+        <v>105.976</v>
       </c>
       <c r="G53">
         <v>1.98</v>
@@ -5761,28 +5761,28 @@
         <v>28.7</v>
       </c>
       <c r="M53">
-        <v>5.7477714</v>
+        <v>5.860472800000001</v>
       </c>
       <c r="N53">
-        <v>22.9522286</v>
+        <v>22.8395272</v>
       </c>
       <c r="O53">
-        <v>3.44283429</v>
+        <v>3.42592908</v>
       </c>
       <c r="P53">
-        <v>19.50939431</v>
+        <v>19.41359812</v>
       </c>
       <c r="Q53">
-        <v>27.80939431</v>
+        <v>27.71359812</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.176727030910135</v>
+        <v>0.179237588035961</v>
       </c>
       <c r="T53">
-        <v>1.706418119636192</v>
+        <v>1.739139095130029</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.993239640671861</v>
+        <v>4.897215801428171</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1104766422572613</v>
+        <v>0.1103844893685564</v>
       </c>
       <c r="C54">
-        <v>140.0992699541184</v>
+        <v>138.4095592177697</v>
       </c>
       <c r="D54">
-        <v>244.0952699541185</v>
+        <v>244.4435592177697</v>
       </c>
       <c r="E54">
-        <v>-21.62399999999998</v>
+        <v>-19.58599999999998</v>
       </c>
       <c r="F54">
-        <v>105.976</v>
+        <v>108.014</v>
       </c>
       <c r="G54">
         <v>1.98</v>
@@ -5843,28 +5843,28 @@
         <v>28.7</v>
       </c>
       <c r="M54">
-        <v>5.860472800000001</v>
+        <v>5.973174200000001</v>
       </c>
       <c r="N54">
-        <v>22.8395272</v>
+        <v>22.7268258</v>
       </c>
       <c r="O54">
-        <v>3.42592908</v>
+        <v>3.40902387</v>
       </c>
       <c r="P54">
-        <v>19.41359812</v>
+        <v>19.31780193</v>
       </c>
       <c r="Q54">
-        <v>27.71359812</v>
+        <v>27.61780193</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.179237588035961</v>
+        <v>0.1818549773799072</v>
       </c>
       <c r="T54">
-        <v>1.739139095130029</v>
+        <v>1.773252452559772</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.897215801428171</v>
+        <v>4.804815503288017</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1103844893685564</v>
+        <v>0.1102923364798515</v>
       </c>
       <c r="C55">
-        <v>138.4095592177697</v>
+        <v>136.7208438202008</v>
       </c>
       <c r="D55">
-        <v>244.4435592177697</v>
+        <v>244.7928438202008</v>
       </c>
       <c r="E55">
-        <v>-19.58599999999998</v>
+        <v>-17.54799999999999</v>
       </c>
       <c r="F55">
-        <v>108.014</v>
+        <v>110.052</v>
       </c>
       <c r="G55">
         <v>1.98</v>
@@ -5925,28 +5925,28 @@
         <v>28.7</v>
       </c>
       <c r="M55">
-        <v>5.973174200000001</v>
+        <v>6.0858756</v>
       </c>
       <c r="N55">
-        <v>22.7268258</v>
+        <v>22.6141244</v>
       </c>
       <c r="O55">
-        <v>3.40902387</v>
+        <v>3.39211866</v>
       </c>
       <c r="P55">
-        <v>19.31780193</v>
+        <v>19.22200574</v>
       </c>
       <c r="Q55">
-        <v>27.61780193</v>
+        <v>27.52200574</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1818549773799072</v>
+        <v>0.1845861662605468</v>
       </c>
       <c r="T55">
-        <v>1.773252452559772</v>
+        <v>1.808848999442983</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.804815503288017</v>
+        <v>4.715837438412313</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1102923364798515</v>
+        <v>0.1102001835911466</v>
       </c>
       <c r="C56">
-        <v>136.7208438202008</v>
+        <v>135.0331280342261</v>
       </c>
       <c r="D56">
-        <v>244.7928438202008</v>
+        <v>245.1431280342262</v>
       </c>
       <c r="E56">
-        <v>-17.54799999999999</v>
+        <v>-15.50999999999998</v>
       </c>
       <c r="F56">
-        <v>110.052</v>
+        <v>112.09</v>
       </c>
       <c r="G56">
         <v>1.98</v>
@@ -6007,28 +6007,28 @@
         <v>28.7</v>
       </c>
       <c r="M56">
-        <v>6.0858756</v>
+        <v>6.198577000000001</v>
       </c>
       <c r="N56">
-        <v>22.6141244</v>
+        <v>22.501423</v>
       </c>
       <c r="O56">
-        <v>3.39211866</v>
+        <v>3.37521345</v>
       </c>
       <c r="P56">
-        <v>19.22200574</v>
+        <v>19.12620955</v>
       </c>
       <c r="Q56">
-        <v>27.52200574</v>
+        <v>27.42620955</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1845861662605468</v>
+        <v>0.1874387413136592</v>
       </c>
       <c r="T56">
-        <v>1.808848999442983</v>
+        <v>1.84602761507656</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.715837438412313</v>
+        <v>4.630094939532089</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1102001835911466</v>
+        <v>0.1101080307024418</v>
       </c>
       <c r="C57">
-        <v>135.0331280342261</v>
+        <v>133.3464161571518</v>
       </c>
       <c r="D57">
-        <v>245.1431280342262</v>
+        <v>245.4944161571518</v>
       </c>
       <c r="E57">
-        <v>-15.50999999999998</v>
+        <v>-13.47199999999998</v>
       </c>
       <c r="F57">
-        <v>112.09</v>
+        <v>114.128</v>
       </c>
       <c r="G57">
         <v>1.98</v>
@@ -6089,28 +6089,28 @@
         <v>28.7</v>
       </c>
       <c r="M57">
-        <v>6.198577000000001</v>
+        <v>6.311278400000001</v>
       </c>
       <c r="N57">
-        <v>22.501423</v>
+        <v>22.3887216</v>
       </c>
       <c r="O57">
-        <v>3.37521345</v>
+        <v>3.35830824</v>
       </c>
       <c r="P57">
-        <v>19.12620955</v>
+        <v>19.03041336</v>
       </c>
       <c r="Q57">
-        <v>27.42620955</v>
+        <v>27.33041336</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1874387413136592</v>
+        <v>0.1904209788691859</v>
       </c>
       <c r="T57">
-        <v>1.84602761507656</v>
+        <v>1.884896167784389</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.630094939532089</v>
+        <v>4.547414672754731</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1101080307024418</v>
+        <v>0.1112271278137369</v>
       </c>
       <c r="C58">
-        <v>133.3464161571518</v>
+        <v>127.1093614050818</v>
       </c>
       <c r="D58">
-        <v>245.4944161571518</v>
+        <v>241.2953614050819</v>
       </c>
       <c r="E58">
-        <v>-13.47199999999998</v>
+        <v>-11.43399999999997</v>
       </c>
       <c r="F58">
-        <v>114.128</v>
+        <v>116.166</v>
       </c>
       <c r="G58">
         <v>1.98</v>
@@ -6171,45 +6171,45 @@
         <v>28.7</v>
       </c>
       <c r="M58">
-        <v>6.311278400000001</v>
+        <v>6.714394800000002</v>
       </c>
       <c r="N58">
-        <v>22.3887216</v>
+        <v>21.9856052</v>
       </c>
       <c r="O58">
-        <v>3.35830824</v>
+        <v>3.29784078</v>
       </c>
       <c r="P58">
-        <v>19.03041336</v>
+        <v>18.68776442</v>
       </c>
       <c r="Q58">
-        <v>27.33041336</v>
+        <v>26.98776442</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1904209788691859</v>
+        <v>0.1935419251482254</v>
       </c>
       <c r="T58">
-        <v>1.884896167784389</v>
+        <v>1.925572560153048</v>
       </c>
       <c r="U58">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V58">
         <v>0.15</v>
       </c>
       <c r="W58">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.547414672754731</v>
+        <v>4.274398639770184</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1112271278137369</v>
+        <v>0.111156224925032</v>
       </c>
       <c r="C59">
-        <v>127.1093614050818</v>
+        <v>125.333135064352</v>
       </c>
       <c r="D59">
-        <v>241.2953614050819</v>
+        <v>241.5571350643521</v>
       </c>
       <c r="E59">
-        <v>-11.43399999999997</v>
+        <v>-9.395999999999972</v>
       </c>
       <c r="F59">
-        <v>116.166</v>
+        <v>118.204</v>
       </c>
       <c r="G59">
         <v>1.98</v>
@@ -6253,28 +6253,28 @@
         <v>28.7</v>
       </c>
       <c r="M59">
-        <v>6.714394800000002</v>
+        <v>6.832191200000001</v>
       </c>
       <c r="N59">
-        <v>21.9856052</v>
+        <v>21.8678088</v>
       </c>
       <c r="O59">
-        <v>3.29784078</v>
+        <v>3.28017132</v>
       </c>
       <c r="P59">
-        <v>18.68776442</v>
+        <v>18.58763748</v>
       </c>
       <c r="Q59">
-        <v>26.98776442</v>
+        <v>26.88763748</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1935419251482254</v>
+        <v>0.1968114879167429</v>
       </c>
       <c r="T59">
-        <v>1.925572560153048</v>
+        <v>1.968185923586881</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.274398639770184</v>
+        <v>4.200702111498284</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.111156224925032</v>
+        <v>0.1110853220363271</v>
       </c>
       <c r="C60">
-        <v>125.333135064352</v>
+        <v>123.5574773203005</v>
       </c>
       <c r="D60">
-        <v>241.557135064352</v>
+        <v>241.8194773203006</v>
       </c>
       <c r="E60">
-        <v>-9.396000000000001</v>
+        <v>-7.35799999999999</v>
       </c>
       <c r="F60">
-        <v>118.204</v>
+        <v>120.242</v>
       </c>
       <c r="G60">
         <v>1.98</v>
@@ -6335,28 +6335,28 @@
         <v>28.7</v>
       </c>
       <c r="M60">
-        <v>6.8321912</v>
+        <v>6.949987600000001</v>
       </c>
       <c r="N60">
-        <v>21.8678088</v>
+        <v>21.7500124</v>
       </c>
       <c r="O60">
-        <v>3.28017132</v>
+        <v>3.26250186</v>
       </c>
       <c r="P60">
-        <v>18.58763748</v>
+        <v>18.48751054</v>
       </c>
       <c r="Q60">
-        <v>26.88763748</v>
+        <v>26.78751054</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1968114879167429</v>
+        <v>0.2002405415520175</v>
       </c>
       <c r="T60">
-        <v>1.968185923586881</v>
+        <v>2.012877987676022</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.200702111498285</v>
+        <v>4.129503770625433</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1110853220363271</v>
+        <v>0.1110144191476223</v>
       </c>
       <c r="C61">
-        <v>123.5574773203005</v>
+        <v>121.7823900275087</v>
       </c>
       <c r="D61">
-        <v>241.8194773203006</v>
+        <v>242.0823900275088</v>
       </c>
       <c r="E61">
-        <v>-7.35799999999999</v>
+        <v>-5.319999999999993</v>
       </c>
       <c r="F61">
-        <v>120.242</v>
+        <v>122.28</v>
       </c>
       <c r="G61">
         <v>1.98</v>
@@ -6417,28 +6417,28 @@
         <v>28.7</v>
       </c>
       <c r="M61">
-        <v>6.949987600000001</v>
+        <v>7.067784000000001</v>
       </c>
       <c r="N61">
-        <v>21.7500124</v>
+        <v>21.632216</v>
       </c>
       <c r="O61">
-        <v>3.26250186</v>
+        <v>3.2448324</v>
       </c>
       <c r="P61">
-        <v>18.48751054</v>
+        <v>18.3873836</v>
       </c>
       <c r="Q61">
-        <v>26.78751054</v>
+        <v>26.6873836</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2002405415520175</v>
+        <v>0.2038410478690557</v>
       </c>
       <c r="T61">
-        <v>2.012877987676022</v>
+        <v>2.059804654969621</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.129503770625433</v>
+        <v>4.060678707781676</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1110144191476223</v>
+        <v>0.1127582662589174</v>
       </c>
       <c r="C62">
-        <v>121.7823900275087</v>
+        <v>113.439646787705</v>
       </c>
       <c r="D62">
-        <v>242.0823900275088</v>
+        <v>235.777646787705</v>
       </c>
       <c r="E62">
-        <v>-5.319999999999993</v>
+        <v>-3.281999999999996</v>
       </c>
       <c r="F62">
-        <v>122.28</v>
+        <v>124.318</v>
       </c>
       <c r="G62">
         <v>1.98</v>
@@ -6499,45 +6499,45 @@
         <v>28.7</v>
       </c>
       <c r="M62">
-        <v>7.067784000000001</v>
+        <v>7.6206934</v>
       </c>
       <c r="N62">
-        <v>21.632216</v>
+        <v>21.0793066</v>
       </c>
       <c r="O62">
-        <v>3.2448324</v>
+        <v>3.16189599</v>
       </c>
       <c r="P62">
-        <v>18.3873836</v>
+        <v>17.91741061</v>
       </c>
       <c r="Q62">
-        <v>26.6873836</v>
+        <v>26.21741061</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2038410478690557</v>
+        <v>0.2076261955356856</v>
       </c>
       <c r="T62">
-        <v>2.059804654969621</v>
+        <v>2.109137818021866</v>
       </c>
       <c r="U62">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V62">
         <v>0.15</v>
       </c>
       <c r="W62">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>4.060678707781676</v>
+        <v>3.766061497763446</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1127582662589174</v>
+        <v>0.1127171133702125</v>
       </c>
       <c r="C63">
-        <v>113.439646787705</v>
+        <v>111.5466460378021</v>
       </c>
       <c r="D63">
-        <v>235.777646787705</v>
+        <v>235.9226460378022</v>
       </c>
       <c r="E63">
-        <v>-3.281999999999996</v>
+        <v>-1.243999999999986</v>
       </c>
       <c r="F63">
-        <v>124.318</v>
+        <v>126.356</v>
       </c>
       <c r="G63">
         <v>1.98</v>
@@ -6581,28 +6581,28 @@
         <v>28.7</v>
       </c>
       <c r="M63">
-        <v>7.6206934</v>
+        <v>7.7456228</v>
       </c>
       <c r="N63">
-        <v>21.0793066</v>
+        <v>20.9543772</v>
       </c>
       <c r="O63">
-        <v>3.16189599</v>
+        <v>3.14315658</v>
       </c>
       <c r="P63">
-        <v>17.91741061</v>
+        <v>17.81122062</v>
       </c>
       <c r="Q63">
-        <v>26.21741061</v>
+        <v>26.11122062</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2076261955356856</v>
+        <v>0.2116105615005593</v>
       </c>
       <c r="T63">
-        <v>2.109137818021866</v>
+        <v>2.161067463340019</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.766061497763446</v>
+        <v>3.705318570380164</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1127171133702125</v>
+        <v>0.1126759604815077</v>
       </c>
       <c r="C64">
-        <v>111.5466460378021</v>
+        <v>109.6538237417999</v>
       </c>
       <c r="D64">
-        <v>235.9226460378022</v>
+        <v>236.0678237417999</v>
       </c>
       <c r="E64">
-        <v>-1.243999999999986</v>
+        <v>0.7940000000000111</v>
       </c>
       <c r="F64">
-        <v>126.356</v>
+        <v>128.394</v>
       </c>
       <c r="G64">
         <v>1.98</v>
@@ -6663,28 +6663,28 @@
         <v>28.7</v>
       </c>
       <c r="M64">
-        <v>7.7456228</v>
+        <v>7.870552200000001</v>
       </c>
       <c r="N64">
-        <v>20.9543772</v>
+        <v>20.8294478</v>
       </c>
       <c r="O64">
-        <v>3.14315658</v>
+        <v>3.124417170000001</v>
       </c>
       <c r="P64">
-        <v>17.81122062</v>
+        <v>17.70503063</v>
       </c>
       <c r="Q64">
-        <v>26.11122062</v>
+        <v>26.00503063</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2116105615005593</v>
+        <v>0.2158102985986694</v>
       </c>
       <c r="T64">
-        <v>2.161067463340019</v>
+        <v>2.215804116513207</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.705318570380164</v>
+        <v>3.646503989897939</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1126759604815077</v>
+        <v>0.1126348075928028</v>
       </c>
       <c r="C65">
-        <v>109.6538237417999</v>
+        <v>107.7611802293422</v>
       </c>
       <c r="D65">
-        <v>236.0678237417999</v>
+        <v>236.2131802293422</v>
       </c>
       <c r="E65">
-        <v>0.7940000000000111</v>
+        <v>2.832000000000022</v>
       </c>
       <c r="F65">
-        <v>128.394</v>
+        <v>130.432</v>
       </c>
       <c r="G65">
         <v>1.98</v>
@@ -6745,28 +6745,28 @@
         <v>28.7</v>
       </c>
       <c r="M65">
-        <v>7.870552200000001</v>
+        <v>7.995481600000001</v>
       </c>
       <c r="N65">
-        <v>20.8294478</v>
+        <v>20.7045184</v>
       </c>
       <c r="O65">
-        <v>3.124417170000001</v>
+        <v>3.10567776</v>
       </c>
       <c r="P65">
-        <v>17.70503063</v>
+        <v>17.59884064</v>
       </c>
       <c r="Q65">
-        <v>26.00503063</v>
+        <v>25.89884064</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2158102985986694</v>
+        <v>0.2202433544244522</v>
       </c>
       <c r="T65">
-        <v>2.215804116513207</v>
+        <v>2.273581694862683</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.646503989897939</v>
+        <v>3.589527365055783</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1126348075928028</v>
+        <v>0.1125936547040979</v>
       </c>
       <c r="C66">
-        <v>107.7611802293422</v>
+        <v>105.8687158308849</v>
       </c>
       <c r="D66">
-        <v>236.2131802293422</v>
+        <v>236.3587158308849</v>
       </c>
       <c r="E66">
-        <v>2.832000000000022</v>
+        <v>4.870000000000005</v>
       </c>
       <c r="F66">
-        <v>130.432</v>
+        <v>132.47</v>
       </c>
       <c r="G66">
         <v>1.98</v>
@@ -6827,28 +6827,28 @@
         <v>28.7</v>
       </c>
       <c r="M66">
-        <v>7.995481600000001</v>
+        <v>8.120411000000001</v>
       </c>
       <c r="N66">
-        <v>20.7045184</v>
+        <v>20.579589</v>
       </c>
       <c r="O66">
-        <v>3.10567776</v>
+        <v>3.08693835</v>
       </c>
       <c r="P66">
-        <v>17.59884064</v>
+        <v>17.49265065</v>
       </c>
       <c r="Q66">
-        <v>25.89884064</v>
+        <v>25.79265065</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2202433544244522</v>
+        <v>0.2249297277259941</v>
       </c>
       <c r="T66">
-        <v>2.273581694862683</v>
+        <v>2.334660849117844</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.589527365055783</v>
+        <v>3.534303867131849</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1125936547040979</v>
+        <v>0.1141233018153931</v>
       </c>
       <c r="C67">
-        <v>105.8687158308849</v>
+        <v>98.53903031081117</v>
       </c>
       <c r="D67">
-        <v>236.3587158308849</v>
+        <v>231.0670303108112</v>
       </c>
       <c r="E67">
-        <v>4.870000000000005</v>
+        <v>6.908000000000015</v>
       </c>
       <c r="F67">
-        <v>132.47</v>
+        <v>134.508</v>
       </c>
       <c r="G67">
         <v>1.98</v>
@@ -6909,45 +6909,45 @@
         <v>28.7</v>
       </c>
       <c r="M67">
-        <v>8.120411000000001</v>
+        <v>8.6219628</v>
       </c>
       <c r="N67">
-        <v>20.579589</v>
+        <v>20.0780372</v>
       </c>
       <c r="O67">
-        <v>3.08693835</v>
+        <v>3.011705580000001</v>
       </c>
       <c r="P67">
-        <v>17.49265065</v>
+        <v>17.06633162</v>
       </c>
       <c r="Q67">
-        <v>25.79265065</v>
+        <v>25.36633162</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2249297277259941</v>
+        <v>0.2298917700452737</v>
       </c>
       <c r="T67">
-        <v>2.334660849117844</v>
+        <v>2.399332894799779</v>
       </c>
       <c r="U67">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V67">
         <v>0.15</v>
       </c>
       <c r="W67">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.534303867131849</v>
+        <v>3.328708400365634</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1141233018153931</v>
+        <v>0.1141059489266882</v>
       </c>
       <c r="C68">
-        <v>98.53903031081117</v>
+        <v>96.55973208603513</v>
       </c>
       <c r="D68">
-        <v>231.0670303108112</v>
+        <v>231.1257320860352</v>
       </c>
       <c r="E68">
-        <v>6.908000000000015</v>
+        <v>8.946000000000026</v>
       </c>
       <c r="F68">
-        <v>134.508</v>
+        <v>136.546</v>
       </c>
       <c r="G68">
         <v>1.98</v>
@@ -6991,28 +6991,28 @@
         <v>28.7</v>
       </c>
       <c r="M68">
-        <v>8.6219628</v>
+        <v>8.752598600000002</v>
       </c>
       <c r="N68">
-        <v>20.0780372</v>
+        <v>19.9474014</v>
       </c>
       <c r="O68">
-        <v>3.011705580000001</v>
+        <v>2.99211021</v>
       </c>
       <c r="P68">
-        <v>17.06633162</v>
+        <v>16.95529119</v>
       </c>
       <c r="Q68">
-        <v>25.36633162</v>
+        <v>25.25529119</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2298917700452737</v>
+        <v>0.2351545422020854</v>
       </c>
       <c r="T68">
-        <v>2.399332894799779</v>
+        <v>2.467924458401831</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.328708400365634</v>
+        <v>3.279026185434803</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1141059489266882</v>
+        <v>0.1140885960379833</v>
       </c>
       <c r="C69">
-        <v>96.55973208603513</v>
+        <v>94.58046369480172</v>
       </c>
       <c r="D69">
-        <v>231.1257320860352</v>
+        <v>231.1844636948018</v>
       </c>
       <c r="E69">
-        <v>8.946000000000026</v>
+        <v>10.98400000000004</v>
       </c>
       <c r="F69">
-        <v>136.546</v>
+        <v>138.584</v>
       </c>
       <c r="G69">
         <v>1.98</v>
@@ -7073,28 +7073,28 @@
         <v>28.7</v>
       </c>
       <c r="M69">
-        <v>8.752598600000002</v>
+        <v>8.883234400000003</v>
       </c>
       <c r="N69">
-        <v>19.9474014</v>
+        <v>19.8167656</v>
       </c>
       <c r="O69">
-        <v>2.99211021</v>
+        <v>2.97251484</v>
       </c>
       <c r="P69">
-        <v>16.95529119</v>
+        <v>16.84425076</v>
       </c>
       <c r="Q69">
-        <v>25.25529119</v>
+        <v>25.14425076</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2351545422020854</v>
+        <v>0.2407462376186979</v>
       </c>
       <c r="T69">
-        <v>2.467924458401831</v>
+        <v>2.540802994729011</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.279026185434803</v>
+        <v>3.230805212119585</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1140885960379833</v>
+        <v>0.1140712431492784</v>
       </c>
       <c r="C70">
-        <v>94.58046369480172</v>
+        <v>92.60122515985981</v>
       </c>
       <c r="D70">
-        <v>231.1844636948018</v>
+        <v>231.2432251598598</v>
       </c>
       <c r="E70">
-        <v>10.98400000000004</v>
+        <v>13.02200000000002</v>
       </c>
       <c r="F70">
-        <v>138.584</v>
+        <v>140.622</v>
       </c>
       <c r="G70">
         <v>1.98</v>
@@ -7155,28 +7155,28 @@
         <v>28.7</v>
       </c>
       <c r="M70">
-        <v>8.883234400000003</v>
+        <v>9.013870200000001</v>
       </c>
       <c r="N70">
-        <v>19.8167656</v>
+        <v>19.6861298</v>
       </c>
       <c r="O70">
-        <v>2.97251484</v>
+        <v>2.95291947</v>
       </c>
       <c r="P70">
-        <v>16.84425076</v>
+        <v>16.73321033</v>
       </c>
       <c r="Q70">
-        <v>25.14425076</v>
+        <v>25.03321033</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2407462376186979</v>
+        <v>0.2466986875783176</v>
       </c>
       <c r="T70">
-        <v>2.540802994729011</v>
+        <v>2.618383372109558</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.230805212119585</v>
+        <v>3.183981948175823</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1140712431492784</v>
+        <v>0.1140538902605736</v>
       </c>
       <c r="C71">
-        <v>92.60122515985981</v>
+        <v>90.62201650398154</v>
       </c>
       <c r="D71">
-        <v>231.2432251598598</v>
+        <v>231.3020165039816</v>
       </c>
       <c r="E71">
-        <v>13.02200000000002</v>
+        <v>15.06000000000003</v>
       </c>
       <c r="F71">
-        <v>140.622</v>
+        <v>142.66</v>
       </c>
       <c r="G71">
         <v>1.98</v>
@@ -7237,28 +7237,28 @@
         <v>28.7</v>
       </c>
       <c r="M71">
-        <v>9.013870200000001</v>
+        <v>9.144506000000002</v>
       </c>
       <c r="N71">
-        <v>19.6861298</v>
+        <v>19.555494</v>
       </c>
       <c r="O71">
-        <v>2.95291947</v>
+        <v>2.933324100000001</v>
       </c>
       <c r="P71">
-        <v>16.73321033</v>
+        <v>16.6221699</v>
       </c>
       <c r="Q71">
-        <v>25.03321033</v>
+        <v>24.9221699</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2466986875783176</v>
+        <v>0.2530479675352452</v>
       </c>
       <c r="T71">
-        <v>2.618383372109558</v>
+        <v>2.701135774648808</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.183981948175823</v>
+        <v>3.138496491773312</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1140538902605736</v>
+        <v>0.1140365373718687</v>
       </c>
       <c r="C72">
-        <v>90.62201650398154</v>
+        <v>88.64283774996196</v>
       </c>
       <c r="D72">
-        <v>231.3020165039816</v>
+        <v>231.360837749962</v>
       </c>
       <c r="E72">
-        <v>15.06000000000003</v>
+        <v>17.09800000000004</v>
       </c>
       <c r="F72">
-        <v>142.66</v>
+        <v>144.698</v>
       </c>
       <c r="G72">
         <v>1.98</v>
@@ -7319,28 +7319,28 @@
         <v>28.7</v>
       </c>
       <c r="M72">
-        <v>9.144506000000002</v>
+        <v>9.275141800000004</v>
       </c>
       <c r="N72">
-        <v>19.555494</v>
+        <v>19.4248582</v>
       </c>
       <c r="O72">
-        <v>2.933324100000001</v>
+        <v>2.91372873</v>
       </c>
       <c r="P72">
-        <v>16.6221699</v>
+        <v>16.51112947</v>
       </c>
       <c r="Q72">
-        <v>24.9221699</v>
+        <v>24.81112947</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2530479675352452</v>
+        <v>0.2598351288685128</v>
       </c>
       <c r="T72">
-        <v>2.701135774648808</v>
+        <v>2.789595239432145</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.138496491773312</v>
+        <v>3.094292315832841</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1140365373718687</v>
+        <v>0.1140191844831638</v>
       </c>
       <c r="C73">
-        <v>88.64283774996198</v>
+        <v>86.66368892061962</v>
       </c>
       <c r="D73">
-        <v>231.360837749962</v>
+        <v>231.4196889206196</v>
       </c>
       <c r="E73">
-        <v>17.09800000000001</v>
+        <v>19.136</v>
       </c>
       <c r="F73">
-        <v>144.698</v>
+        <v>146.736</v>
       </c>
       <c r="G73">
         <v>1.98</v>
@@ -7401,28 +7401,28 @@
         <v>28.7</v>
       </c>
       <c r="M73">
-        <v>9.275141800000002</v>
+        <v>9.4057776</v>
       </c>
       <c r="N73">
-        <v>19.4248582</v>
+        <v>19.2942224</v>
       </c>
       <c r="O73">
-        <v>2.91372873</v>
+        <v>2.89413336</v>
       </c>
       <c r="P73">
-        <v>16.51112947</v>
+        <v>16.40008904</v>
       </c>
       <c r="Q73">
-        <v>24.81112947</v>
+        <v>24.70008904</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2598351288685127</v>
+        <v>0.2671070874398708</v>
       </c>
       <c r="T73">
-        <v>2.789595239432144</v>
+        <v>2.884373237414289</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.094292315832842</v>
+        <v>3.051316033668498</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1140191844831638</v>
+        <v>0.114001831594459</v>
       </c>
       <c r="C74">
-        <v>86.66368892061962</v>
+        <v>84.6845700387959</v>
       </c>
       <c r="D74">
-        <v>231.4196889206196</v>
+        <v>231.4785700387959</v>
       </c>
       <c r="E74">
-        <v>19.136</v>
+        <v>21.17400000000001</v>
       </c>
       <c r="F74">
-        <v>146.736</v>
+        <v>148.774</v>
       </c>
       <c r="G74">
         <v>1.98</v>
@@ -7483,28 +7483,28 @@
         <v>28.7</v>
       </c>
       <c r="M74">
-        <v>9.4057776</v>
+        <v>9.536413400000001</v>
       </c>
       <c r="N74">
-        <v>19.2942224</v>
+        <v>19.1635866</v>
       </c>
       <c r="O74">
-        <v>2.89413336</v>
+        <v>2.87453799</v>
       </c>
       <c r="P74">
-        <v>16.40008904</v>
+        <v>16.28904861</v>
       </c>
       <c r="Q74">
-        <v>24.70008904</v>
+        <v>24.58904861</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2671070874398708</v>
+        <v>0.2749177096091072</v>
       </c>
       <c r="T74">
-        <v>2.884373237414289</v>
+        <v>2.986171827839557</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.051316033668498</v>
+        <v>3.009517183892217</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.114001831594459</v>
+        <v>0.1188906787057541</v>
       </c>
       <c r="C75">
-        <v>84.6845700387959</v>
+        <v>67.16356511259039</v>
       </c>
       <c r="D75">
-        <v>231.4785700387959</v>
+        <v>215.9955651125904</v>
       </c>
       <c r="E75">
-        <v>21.17400000000001</v>
+        <v>23.21200000000002</v>
       </c>
       <c r="F75">
-        <v>148.774</v>
+        <v>150.812</v>
       </c>
       <c r="G75">
         <v>1.98</v>
@@ -7565,45 +7565,45 @@
         <v>28.7</v>
       </c>
       <c r="M75">
-        <v>9.536413400000001</v>
+        <v>10.8433828</v>
       </c>
       <c r="N75">
-        <v>19.1635866</v>
+        <v>17.8566172</v>
       </c>
       <c r="O75">
-        <v>2.87453799</v>
+        <v>2.67849258</v>
       </c>
       <c r="P75">
-        <v>16.28904861</v>
+        <v>15.17812462</v>
       </c>
       <c r="Q75">
-        <v>24.58904861</v>
+        <v>23.47812462</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2749177096091072</v>
+        <v>0.2833291488682849</v>
       </c>
       <c r="T75">
-        <v>2.986171827839557</v>
+        <v>3.095801079066768</v>
       </c>
       <c r="U75">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V75">
         <v>0.15</v>
       </c>
       <c r="W75">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y75">
-        <v>3.009517183892217</v>
+        <v>2.646775506256221</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1188906787057541</v>
+        <v>0.1189396258170492</v>
       </c>
       <c r="C76">
-        <v>67.16356511259039</v>
+        <v>64.98101475638177</v>
       </c>
       <c r="D76">
-        <v>215.9955651125904</v>
+        <v>215.8510147563818</v>
       </c>
       <c r="E76">
-        <v>23.21200000000002</v>
+        <v>25.25000000000003</v>
       </c>
       <c r="F76">
-        <v>150.812</v>
+        <v>152.85</v>
       </c>
       <c r="G76">
         <v>1.98</v>
@@ -7647,28 +7647,28 @@
         <v>28.7</v>
       </c>
       <c r="M76">
-        <v>10.8433828</v>
+        <v>10.989915</v>
       </c>
       <c r="N76">
-        <v>17.8566172</v>
+        <v>17.710085</v>
       </c>
       <c r="O76">
-        <v>2.67849258</v>
+        <v>2.65651275</v>
       </c>
       <c r="P76">
-        <v>15.17812462</v>
+        <v>15.05357225</v>
       </c>
       <c r="Q76">
-        <v>23.47812462</v>
+        <v>23.35357225</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2833291488682849</v>
+        <v>0.2924135032681968</v>
       </c>
       <c r="T76">
-        <v>3.095801079066768</v>
+        <v>3.214200670392156</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.646775506256221</v>
+        <v>2.611485166172804</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1189396258170492</v>
+        <v>0.1189885729283443</v>
       </c>
       <c r="C77">
-        <v>64.98101475638177</v>
+        <v>62.79865774517467</v>
       </c>
       <c r="D77">
-        <v>215.8510147563818</v>
+        <v>215.7066577451747</v>
       </c>
       <c r="E77">
-        <v>25.25000000000003</v>
+        <v>27.28800000000001</v>
       </c>
       <c r="F77">
-        <v>152.85</v>
+        <v>154.888</v>
       </c>
       <c r="G77">
         <v>1.98</v>
@@ -7729,28 +7729,28 @@
         <v>28.7</v>
       </c>
       <c r="M77">
-        <v>10.989915</v>
+        <v>11.1364472</v>
       </c>
       <c r="N77">
-        <v>17.710085</v>
+        <v>17.5635528</v>
       </c>
       <c r="O77">
-        <v>2.65651275</v>
+        <v>2.63453292</v>
       </c>
       <c r="P77">
-        <v>15.05357225</v>
+        <v>14.92901988</v>
       </c>
       <c r="Q77">
-        <v>23.35357225</v>
+        <v>23.22901988</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2924135032681968</v>
+        <v>0.3022548872014348</v>
       </c>
       <c r="T77">
-        <v>3.214200670392156</v>
+        <v>3.342466894327994</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.611485166172804</v>
+        <v>2.577123519249478</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1189885729283443</v>
+        <v>0.1190375200396395</v>
       </c>
       <c r="C78">
-        <v>62.79865774517467</v>
+        <v>60.61649369131217</v>
       </c>
       <c r="D78">
-        <v>215.7066577451747</v>
+        <v>215.5624936913122</v>
       </c>
       <c r="E78">
-        <v>27.28800000000001</v>
+        <v>29.32600000000002</v>
       </c>
       <c r="F78">
-        <v>154.888</v>
+        <v>156.926</v>
       </c>
       <c r="G78">
         <v>1.98</v>
@@ -7811,28 +7811,28 @@
         <v>28.7</v>
       </c>
       <c r="M78">
-        <v>11.1364472</v>
+        <v>11.2829794</v>
       </c>
       <c r="N78">
-        <v>17.5635528</v>
+        <v>17.4170206</v>
       </c>
       <c r="O78">
-        <v>2.63453292</v>
+        <v>2.61255309</v>
       </c>
       <c r="P78">
-        <v>14.92901988</v>
+        <v>14.80446751</v>
       </c>
       <c r="Q78">
-        <v>23.22901988</v>
+        <v>23.10446751</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3022548872014348</v>
+        <v>0.3129520436506064</v>
       </c>
       <c r="T78">
-        <v>3.342466894327994</v>
+        <v>3.481886702953904</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.577123519249478</v>
+        <v>2.543654382635848</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1190375200396395</v>
+        <v>0.1190864671509346</v>
       </c>
       <c r="C79">
-        <v>60.61649369131217</v>
+        <v>58.43452220817278</v>
       </c>
       <c r="D79">
-        <v>215.5624936913122</v>
+        <v>215.4185222081728</v>
       </c>
       <c r="E79">
-        <v>29.32600000000002</v>
+        <v>31.36400000000003</v>
       </c>
       <c r="F79">
-        <v>156.926</v>
+        <v>158.964</v>
       </c>
       <c r="G79">
         <v>1.98</v>
@@ -7893,28 +7893,28 @@
         <v>28.7</v>
       </c>
       <c r="M79">
-        <v>11.2829794</v>
+        <v>11.4295116</v>
       </c>
       <c r="N79">
-        <v>17.4170206</v>
+        <v>17.2704884</v>
       </c>
       <c r="O79">
-        <v>2.61255309</v>
+        <v>2.59057326</v>
       </c>
       <c r="P79">
-        <v>14.80446751</v>
+        <v>14.67991514</v>
       </c>
       <c r="Q79">
-        <v>23.10446751</v>
+        <v>22.97991514</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3129520436506064</v>
+        <v>0.3246216688678845</v>
       </c>
       <c r="T79">
-        <v>3.481886702953904</v>
+        <v>3.633981039636715</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.543654382635848</v>
+        <v>2.511043429012312</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1190864671509346</v>
+        <v>0.1217542642622297</v>
       </c>
       <c r="C80">
-        <v>58.43452220817278</v>
+        <v>48.83022008085155</v>
       </c>
       <c r="D80">
-        <v>215.4185222081728</v>
+        <v>207.8522200808516</v>
       </c>
       <c r="E80">
-        <v>31.36400000000003</v>
+        <v>33.40200000000002</v>
       </c>
       <c r="F80">
-        <v>158.964</v>
+        <v>161.002</v>
       </c>
       <c r="G80">
         <v>1.98</v>
@@ -7975,45 +7975,45 @@
         <v>28.7</v>
       </c>
       <c r="M80">
-        <v>11.4295116</v>
+        <v>12.2039516</v>
       </c>
       <c r="N80">
-        <v>17.2704884</v>
+        <v>16.4960484</v>
       </c>
       <c r="O80">
-        <v>2.59057326</v>
+        <v>2.47440726</v>
       </c>
       <c r="P80">
-        <v>14.67991514</v>
+        <v>14.02164114</v>
       </c>
       <c r="Q80">
-        <v>22.97991514</v>
+        <v>22.32164114</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3246216688678845</v>
+        <v>0.3374026869629987</v>
       </c>
       <c r="T80">
-        <v>3.633981039636715</v>
+        <v>3.800560551241698</v>
       </c>
       <c r="U80">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V80">
         <v>0.15</v>
       </c>
       <c r="W80">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y80">
-        <v>2.511043429012312</v>
+        <v>2.351697297783449</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1217542642622297</v>
+        <v>0.1218363613735249</v>
       </c>
       <c r="C81">
-        <v>48.83022008085155</v>
+        <v>46.56780025674803</v>
       </c>
       <c r="D81">
-        <v>207.8522200808516</v>
+        <v>207.6278002567481</v>
       </c>
       <c r="E81">
-        <v>33.40200000000002</v>
+        <v>35.44000000000003</v>
       </c>
       <c r="F81">
-        <v>161.002</v>
+        <v>163.04</v>
       </c>
       <c r="G81">
         <v>1.98</v>
@@ -8057,28 +8057,28 @@
         <v>28.7</v>
       </c>
       <c r="M81">
-        <v>12.2039516</v>
+        <v>12.358432</v>
       </c>
       <c r="N81">
-        <v>16.4960484</v>
+        <v>16.341568</v>
       </c>
       <c r="O81">
-        <v>2.47440726</v>
+        <v>2.4512352</v>
       </c>
       <c r="P81">
-        <v>14.02164114</v>
+        <v>13.8903328</v>
       </c>
       <c r="Q81">
-        <v>22.32164114</v>
+        <v>22.1903328</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3374026869629987</v>
+        <v>0.3514618068676243</v>
       </c>
       <c r="T81">
-        <v>3.800560551241698</v>
+        <v>3.98379801400718</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.351697297783449</v>
+        <v>2.322301081561156</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1218363613735249</v>
+        <v>0.12191845848482</v>
       </c>
       <c r="C82">
-        <v>46.56780025674803</v>
+        <v>44.30586452598121</v>
       </c>
       <c r="D82">
-        <v>207.6278002567481</v>
+        <v>207.4038645259812</v>
       </c>
       <c r="E82">
-        <v>35.44000000000003</v>
+        <v>37.47800000000004</v>
       </c>
       <c r="F82">
-        <v>163.04</v>
+        <v>165.078</v>
       </c>
       <c r="G82">
         <v>1.98</v>
@@ -8139,28 +8139,28 @@
         <v>28.7</v>
       </c>
       <c r="M82">
-        <v>12.358432</v>
+        <v>12.5129124</v>
       </c>
       <c r="N82">
-        <v>16.341568</v>
+        <v>16.1870876</v>
       </c>
       <c r="O82">
-        <v>2.4512352</v>
+        <v>2.428063139999999</v>
       </c>
       <c r="P82">
-        <v>13.8903328</v>
+        <v>13.75902446</v>
       </c>
       <c r="Q82">
-        <v>22.1903328</v>
+        <v>22.05902446</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3514618068676243</v>
+        <v>0.3670008341306316</v>
       </c>
       <c r="T82">
-        <v>3.98379801400718</v>
+        <v>4.186323630747977</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.322301081561156</v>
+        <v>2.293630697838178</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.12191845848482</v>
+        <v>0.1220005555961151</v>
       </c>
       <c r="C83">
-        <v>44.30586452598121</v>
+        <v>42.04441132389073</v>
       </c>
       <c r="D83">
-        <v>207.4038645259812</v>
+        <v>207.1804113238908</v>
       </c>
       <c r="E83">
-        <v>37.47800000000004</v>
+        <v>39.51600000000002</v>
       </c>
       <c r="F83">
-        <v>165.078</v>
+        <v>167.116</v>
       </c>
       <c r="G83">
         <v>1.98</v>
@@ -8221,28 +8221,28 @@
         <v>28.7</v>
       </c>
       <c r="M83">
-        <v>12.5129124</v>
+        <v>12.6673928</v>
       </c>
       <c r="N83">
-        <v>16.1870876</v>
+        <v>16.0326072</v>
       </c>
       <c r="O83">
-        <v>2.428063139999999</v>
+        <v>2.40489108</v>
       </c>
       <c r="P83">
-        <v>13.75902446</v>
+        <v>13.62771612</v>
       </c>
       <c r="Q83">
-        <v>22.05902446</v>
+        <v>21.92771612</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3670008341306316</v>
+        <v>0.3842664199784173</v>
       </c>
       <c r="T83">
-        <v>4.186323630747977</v>
+        <v>4.411352093793306</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.293630697838178</v>
+        <v>2.265659591766982</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1220005555961151</v>
+        <v>0.1220826527074102</v>
       </c>
       <c r="C84">
-        <v>42.04441132389073</v>
+        <v>39.78343909255173</v>
       </c>
       <c r="D84">
-        <v>207.1804113238908</v>
+        <v>206.9574390925518</v>
       </c>
       <c r="E84">
-        <v>39.51600000000002</v>
+        <v>41.55400000000003</v>
       </c>
       <c r="F84">
-        <v>167.116</v>
+        <v>169.154</v>
       </c>
       <c r="G84">
         <v>1.98</v>
@@ -8303,28 +8303,28 @@
         <v>28.7</v>
       </c>
       <c r="M84">
-        <v>12.6673928</v>
+        <v>12.8218732</v>
       </c>
       <c r="N84">
-        <v>16.0326072</v>
+        <v>15.8781268</v>
       </c>
       <c r="O84">
-        <v>2.40489108</v>
+        <v>2.38171902</v>
       </c>
       <c r="P84">
-        <v>13.62771612</v>
+        <v>13.49640778</v>
       </c>
       <c r="Q84">
-        <v>21.92771612</v>
+        <v>21.79640778</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3842664199784173</v>
+        <v>0.4035632512200603</v>
       </c>
       <c r="T84">
-        <v>4.411352093793306</v>
+        <v>4.662854493667496</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.265659591766982</v>
+        <v>2.238362488251716</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1220826527074102</v>
+        <v>0.1221647498187054</v>
       </c>
       <c r="C85">
-        <v>39.78343909255173</v>
+        <v>37.52294628073898</v>
       </c>
       <c r="D85">
-        <v>206.9574390925518</v>
+        <v>206.734946280739</v>
       </c>
       <c r="E85">
-        <v>41.55400000000003</v>
+        <v>43.59200000000004</v>
       </c>
       <c r="F85">
-        <v>169.154</v>
+        <v>171.192</v>
       </c>
       <c r="G85">
         <v>1.98</v>
@@ -8385,28 +8385,28 @@
         <v>28.7</v>
       </c>
       <c r="M85">
-        <v>12.8218732</v>
+        <v>12.9763536</v>
       </c>
       <c r="N85">
-        <v>15.8781268</v>
+        <v>15.7236464</v>
       </c>
       <c r="O85">
-        <v>2.38171902</v>
+        <v>2.35854696</v>
       </c>
       <c r="P85">
-        <v>13.49640778</v>
+        <v>13.36509944</v>
       </c>
       <c r="Q85">
-        <v>21.79640778</v>
+        <v>21.66509944</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4035632512200603</v>
+        <v>0.4252721863669087</v>
       </c>
       <c r="T85">
-        <v>4.662854493667496</v>
+        <v>4.945794693525962</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.238362488251716</v>
+        <v>2.211715315772529</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1221647498187054</v>
+        <v>0.1222468469300005</v>
       </c>
       <c r="C86">
-        <v>37.52294628073901</v>
+        <v>35.26293134389093</v>
       </c>
       <c r="D86">
-        <v>206.734946280739</v>
+        <v>206.512931343891</v>
       </c>
       <c r="E86">
-        <v>43.59200000000001</v>
+        <v>45.63000000000002</v>
       </c>
       <c r="F86">
-        <v>171.192</v>
+        <v>173.23</v>
       </c>
       <c r="G86">
         <v>1.98</v>
@@ -8467,28 +8467,28 @@
         <v>28.7</v>
       </c>
       <c r="M86">
-        <v>12.9763536</v>
+        <v>13.130834</v>
       </c>
       <c r="N86">
-        <v>15.7236464</v>
+        <v>15.569166</v>
       </c>
       <c r="O86">
-        <v>2.35854696</v>
+        <v>2.3353749</v>
       </c>
       <c r="P86">
-        <v>13.36509944</v>
+        <v>13.2337911</v>
       </c>
       <c r="Q86">
-        <v>21.66509944</v>
+        <v>21.5337911</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4252721863669084</v>
+        <v>0.4498756462000032</v>
       </c>
       <c r="T86">
-        <v>4.945794693525959</v>
+        <v>5.266460253365552</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.21171531577253</v>
+        <v>2.18569513558697</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1222468469300005</v>
+        <v>0.1223289440412956</v>
       </c>
       <c r="C87">
-        <v>35.26293134389093</v>
+        <v>33.00339274407341</v>
       </c>
       <c r="D87">
-        <v>206.512931343891</v>
+        <v>206.2913927440734</v>
       </c>
       <c r="E87">
-        <v>45.63000000000002</v>
+        <v>47.66800000000001</v>
       </c>
       <c r="F87">
-        <v>173.23</v>
+        <v>175.268</v>
       </c>
       <c r="G87">
         <v>1.98</v>
@@ -8549,28 +8549,28 @@
         <v>28.7</v>
       </c>
       <c r="M87">
-        <v>13.130834</v>
+        <v>13.2853144</v>
       </c>
       <c r="N87">
-        <v>15.569166</v>
+        <v>15.4146856</v>
       </c>
       <c r="O87">
-        <v>2.3353749</v>
+        <v>2.31220284</v>
       </c>
       <c r="P87">
-        <v>13.2337911</v>
+        <v>13.10248276</v>
       </c>
       <c r="Q87">
-        <v>21.5337911</v>
+        <v>21.40248276</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4498756462000032</v>
+        <v>0.4779938860092544</v>
       </c>
       <c r="T87">
-        <v>5.266460253365552</v>
+        <v>5.632935178896515</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.18569513558697</v>
+        <v>2.160280075870843</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1223289440412956</v>
+        <v>0.1224110411525907</v>
       </c>
       <c r="C88">
-        <v>33.00339274407341</v>
+        <v>30.74432894994476</v>
       </c>
       <c r="D88">
-        <v>206.2913927440734</v>
+        <v>206.0703289499448</v>
       </c>
       <c r="E88">
-        <v>47.66800000000001</v>
+        <v>49.70600000000002</v>
       </c>
       <c r="F88">
-        <v>175.268</v>
+        <v>177.306</v>
       </c>
       <c r="G88">
         <v>1.98</v>
@@ -8631,28 +8631,28 @@
         <v>28.7</v>
       </c>
       <c r="M88">
-        <v>13.2853144</v>
+        <v>13.4397948</v>
       </c>
       <c r="N88">
-        <v>15.4146856</v>
+        <v>15.2602052</v>
       </c>
       <c r="O88">
-        <v>2.31220284</v>
+        <v>2.28903078</v>
       </c>
       <c r="P88">
-        <v>13.10248276</v>
+        <v>12.97117442</v>
       </c>
       <c r="Q88">
-        <v>21.40248276</v>
+        <v>21.27117442</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4779938860092544</v>
+        <v>0.5104380088660826</v>
       </c>
       <c r="T88">
-        <v>5.632935178896515</v>
+        <v>6.055790862201474</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.160280075870843</v>
+        <v>2.135449270401063</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1224110411525907</v>
+        <v>0.1224931382638859</v>
       </c>
       <c r="C89">
-        <v>30.74432894994476</v>
+        <v>28.48573843672028</v>
       </c>
       <c r="D89">
-        <v>206.0703289499448</v>
+        <v>205.8497384367203</v>
       </c>
       <c r="E89">
-        <v>49.70600000000002</v>
+        <v>51.74400000000003</v>
       </c>
       <c r="F89">
-        <v>177.306</v>
+        <v>179.344</v>
       </c>
       <c r="G89">
         <v>1.98</v>
@@ -8713,28 +8713,28 @@
         <v>28.7</v>
       </c>
       <c r="M89">
-        <v>13.4397948</v>
+        <v>13.5942752</v>
       </c>
       <c r="N89">
-        <v>15.2602052</v>
+        <v>15.1057248</v>
       </c>
       <c r="O89">
-        <v>2.28903078</v>
+        <v>2.26585872</v>
       </c>
       <c r="P89">
-        <v>12.97117442</v>
+        <v>12.83986608</v>
       </c>
       <c r="Q89">
-        <v>21.27117442</v>
+        <v>21.13986608</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5104380088660826</v>
+        <v>0.5482894855323822</v>
       </c>
       <c r="T89">
-        <v>6.055790862201474</v>
+        <v>6.549122492723925</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.135449270401063</v>
+        <v>2.111182801419233</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1224931382638859</v>
+        <v>0.122575235375181</v>
       </c>
       <c r="C90">
-        <v>28.48573843672028</v>
+        <v>26.22761968613713</v>
       </c>
       <c r="D90">
-        <v>205.8497384367203</v>
+        <v>205.6296196861371</v>
       </c>
       <c r="E90">
-        <v>51.74400000000003</v>
+        <v>53.78200000000001</v>
       </c>
       <c r="F90">
-        <v>179.344</v>
+        <v>181.382</v>
       </c>
       <c r="G90">
         <v>1.98</v>
@@ -8795,28 +8795,28 @@
         <v>28.7</v>
       </c>
       <c r="M90">
-        <v>13.5942752</v>
+        <v>13.7487556</v>
       </c>
       <c r="N90">
-        <v>15.1057248</v>
+        <v>14.9512444</v>
       </c>
       <c r="O90">
-        <v>2.26585872</v>
+        <v>2.24268666</v>
       </c>
       <c r="P90">
-        <v>12.83986608</v>
+        <v>12.70855774</v>
       </c>
       <c r="Q90">
-        <v>21.13986608</v>
+        <v>21.00855774</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5482894855323822</v>
+        <v>0.5930230488652818</v>
       </c>
       <c r="T90">
-        <v>6.549122492723925</v>
+        <v>7.132150783341367</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.111182801419233</v>
+        <v>2.087461646347107</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.122575235375181</v>
+        <v>0.1226573324864761</v>
       </c>
       <c r="C91">
-        <v>26.22761968613713</v>
+        <v>23.96997118641949</v>
       </c>
       <c r="D91">
-        <v>205.6296196861371</v>
+        <v>205.4099711864195</v>
       </c>
       <c r="E91">
-        <v>53.78200000000001</v>
+        <v>55.82000000000002</v>
       </c>
       <c r="F91">
-        <v>181.382</v>
+        <v>183.42</v>
       </c>
       <c r="G91">
         <v>1.98</v>
@@ -8877,28 +8877,28 @@
         <v>28.7</v>
       </c>
       <c r="M91">
-        <v>13.7487556</v>
+        <v>13.903236</v>
       </c>
       <c r="N91">
-        <v>14.9512444</v>
+        <v>14.796764</v>
       </c>
       <c r="O91">
-        <v>2.24268666</v>
+        <v>2.2195146</v>
       </c>
       <c r="P91">
-        <v>12.70855774</v>
+        <v>12.5772494</v>
       </c>
       <c r="Q91">
-        <v>21.00855774</v>
+        <v>20.8772494</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5930230488652818</v>
+        <v>0.6467033248647615</v>
       </c>
       <c r="T91">
-        <v>7.132150783341367</v>
+        <v>7.8317847320823</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.087461646347107</v>
+        <v>2.064267628054361</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1226573324864761</v>
+        <v>0.1227394295977713</v>
       </c>
       <c r="C92">
-        <v>23.96997118641949</v>
+        <v>21.71279143224433</v>
       </c>
       <c r="D92">
-        <v>205.4099711864195</v>
+        <v>205.1907914322444</v>
       </c>
       <c r="E92">
-        <v>55.82000000000002</v>
+        <v>57.85800000000003</v>
       </c>
       <c r="F92">
-        <v>183.42</v>
+        <v>185.458</v>
       </c>
       <c r="G92">
         <v>1.98</v>
@@ -8959,28 +8959,28 @@
         <v>28.7</v>
       </c>
       <c r="M92">
-        <v>13.903236</v>
+        <v>14.0577164</v>
       </c>
       <c r="N92">
-        <v>14.796764</v>
+        <v>14.6422836</v>
       </c>
       <c r="O92">
-        <v>2.2195146</v>
+        <v>2.19634254</v>
       </c>
       <c r="P92">
-        <v>12.5772494</v>
+        <v>12.44594106</v>
       </c>
       <c r="Q92">
-        <v>20.8772494</v>
+        <v>20.74594106</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6467033248647615</v>
+        <v>0.7123125510863474</v>
       </c>
       <c r="T92">
-        <v>7.8317847320823</v>
+        <v>8.686892891654548</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.064267628054361</v>
+        <v>2.041583368405411</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1227394295977713</v>
+        <v>0.1228215267090664</v>
       </c>
       <c r="C93">
-        <v>21.71279143224433</v>
+        <v>19.45607892470633</v>
       </c>
       <c r="D93">
-        <v>205.1907914322444</v>
+        <v>204.9720789247064</v>
       </c>
       <c r="E93">
-        <v>57.85800000000003</v>
+        <v>59.89600000000002</v>
       </c>
       <c r="F93">
-        <v>185.458</v>
+        <v>187.496</v>
       </c>
       <c r="G93">
         <v>1.98</v>
@@ -9041,28 +9041,28 @@
         <v>28.7</v>
       </c>
       <c r="M93">
-        <v>14.0577164</v>
+        <v>14.2121968</v>
       </c>
       <c r="N93">
-        <v>14.6422836</v>
+        <v>14.4878032</v>
       </c>
       <c r="O93">
-        <v>2.19634254</v>
+        <v>2.17317048</v>
       </c>
       <c r="P93">
-        <v>12.44594106</v>
+        <v>12.31463272</v>
       </c>
       <c r="Q93">
-        <v>20.74594106</v>
+        <v>20.61463272</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7123125510863474</v>
+        <v>0.7943240838633302</v>
       </c>
       <c r="T93">
-        <v>8.686892891654548</v>
+        <v>9.755778091119861</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.041583368405411</v>
+        <v>2.019392244835788</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1228215267090664</v>
+        <v>0.1341287238203615</v>
       </c>
       <c r="C94">
-        <v>19.45607892470633</v>
+        <v>-8.820947277315298</v>
       </c>
       <c r="D94">
-        <v>204.9720789247064</v>
+        <v>178.7330527226847</v>
       </c>
       <c r="E94">
-        <v>59.89600000000002</v>
+        <v>61.93400000000003</v>
       </c>
       <c r="F94">
-        <v>187.496</v>
+        <v>189.534</v>
       </c>
       <c r="G94">
         <v>1.98</v>
@@ -9123,45 +9123,45 @@
         <v>28.7</v>
       </c>
       <c r="M94">
-        <v>14.2121968</v>
+        <v>17.05806</v>
       </c>
       <c r="N94">
-        <v>14.4878032</v>
+        <v>11.64194</v>
       </c>
       <c r="O94">
-        <v>2.17317048</v>
+        <v>1.746291</v>
       </c>
       <c r="P94">
-        <v>12.31463272</v>
+        <v>9.895649000000002</v>
       </c>
       <c r="Q94">
-        <v>20.61463272</v>
+        <v>18.195649</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7943240838633302</v>
+        <v>0.8997674831480222</v>
       </c>
       <c r="T94">
-        <v>9.755778091119861</v>
+        <v>11.13005906186098</v>
       </c>
       <c r="U94">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V94">
         <v>0.15</v>
       </c>
       <c r="W94">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.019392244835788</v>
+        <v>1.682489098994845</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1341287238203615</v>
+        <v>0.1343315209316566</v>
       </c>
       <c r="C95">
-        <v>-8.820947277315298</v>
+        <v>-11.26836695522979</v>
       </c>
       <c r="D95">
-        <v>178.7330527226847</v>
+        <v>178.3236330447702</v>
       </c>
       <c r="E95">
-        <v>61.93400000000003</v>
+        <v>63.97200000000004</v>
       </c>
       <c r="F95">
-        <v>189.534</v>
+        <v>191.572</v>
       </c>
       <c r="G95">
         <v>1.98</v>
@@ -9205,28 +9205,28 @@
         <v>28.7</v>
       </c>
       <c r="M95">
-        <v>17.05806</v>
+        <v>17.24148</v>
       </c>
       <c r="N95">
-        <v>11.64194</v>
+        <v>11.45852</v>
       </c>
       <c r="O95">
-        <v>1.746291</v>
+        <v>1.718778</v>
       </c>
       <c r="P95">
-        <v>9.895649000000002</v>
+        <v>9.739742</v>
       </c>
       <c r="Q95">
-        <v>18.195649</v>
+        <v>18.039742</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8997674831480222</v>
+        <v>1.040358682194278</v>
       </c>
       <c r="T95">
-        <v>11.13005906186098</v>
+        <v>12.9624336895158</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.682489098994845</v>
+        <v>1.664590278792772</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1343315209316566</v>
+        <v>0.1345343180429518</v>
       </c>
       <c r="C96">
-        <v>-11.26836695522979</v>
+        <v>-13.71391522352926</v>
       </c>
       <c r="D96">
-        <v>178.3236330447702</v>
+        <v>177.9160847764708</v>
       </c>
       <c r="E96">
-        <v>63.97200000000004</v>
+        <v>66.01000000000002</v>
       </c>
       <c r="F96">
-        <v>191.572</v>
+        <v>193.61</v>
       </c>
       <c r="G96">
         <v>1.98</v>
@@ -9287,28 +9287,28 @@
         <v>28.7</v>
       </c>
       <c r="M96">
-        <v>17.24148</v>
+        <v>17.4249</v>
       </c>
       <c r="N96">
-        <v>11.45852</v>
+        <v>11.2751</v>
       </c>
       <c r="O96">
-        <v>1.718778</v>
+        <v>1.691265</v>
       </c>
       <c r="P96">
-        <v>9.739742</v>
+        <v>9.583835000000002</v>
       </c>
       <c r="Q96">
-        <v>18.039742</v>
+        <v>17.883835</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.040358682194278</v>
+        <v>1.237186360859037</v>
       </c>
       <c r="T96">
-        <v>12.9624336895158</v>
+        <v>15.52775816823255</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.664590278792772</v>
+        <v>1.647068275858111</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1345343180429518</v>
+        <v>0.1347371151542469</v>
       </c>
       <c r="C97">
-        <v>-13.71391522352926</v>
+        <v>-16.15760488394864</v>
       </c>
       <c r="D97">
-        <v>177.9160847764708</v>
+        <v>177.5103951160514</v>
       </c>
       <c r="E97">
-        <v>66.01000000000002</v>
+        <v>68.04800000000003</v>
       </c>
       <c r="F97">
-        <v>193.61</v>
+        <v>195.648</v>
       </c>
       <c r="G97">
         <v>1.98</v>
@@ -9369,28 +9369,28 @@
         <v>28.7</v>
       </c>
       <c r="M97">
-        <v>17.4249</v>
+        <v>17.60832</v>
       </c>
       <c r="N97">
-        <v>11.2751</v>
+        <v>11.09168</v>
       </c>
       <c r="O97">
-        <v>1.691265</v>
+        <v>1.663752</v>
       </c>
       <c r="P97">
-        <v>9.583835000000002</v>
+        <v>9.427928</v>
       </c>
       <c r="Q97">
-        <v>17.883835</v>
+        <v>17.727928</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.237186360859037</v>
+        <v>1.532427878856175</v>
       </c>
       <c r="T97">
-        <v>15.52775816823255</v>
+        <v>19.37574488630768</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.647068275858111</v>
+        <v>1.629911314651256</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1347371151542469</v>
+        <v>0.134939912265542</v>
       </c>
       <c r="C98">
-        <v>-16.15760488394855</v>
+        <v>-18.59944862172517</v>
       </c>
       <c r="D98">
-        <v>177.5103951160515</v>
+        <v>177.1065513782748</v>
       </c>
       <c r="E98">
-        <v>68.048</v>
+        <v>70.08600000000001</v>
       </c>
       <c r="F98">
-        <v>195.648</v>
+        <v>197.686</v>
       </c>
       <c r="G98">
         <v>1.98</v>
@@ -9451,28 +9451,28 @@
         <v>28.7</v>
       </c>
       <c r="M98">
-        <v>17.60832</v>
+        <v>17.79174</v>
       </c>
       <c r="N98">
-        <v>11.09168</v>
+        <v>10.90826</v>
       </c>
       <c r="O98">
-        <v>1.663752000000001</v>
+        <v>1.636239</v>
       </c>
       <c r="P98">
-        <v>9.427928000000003</v>
+        <v>9.272021000000002</v>
       </c>
       <c r="Q98">
-        <v>17.727928</v>
+        <v>17.572021</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.532427878856171</v>
+        <v>2.024497075518066</v>
       </c>
       <c r="T98">
-        <v>19.37574488630763</v>
+        <v>25.78905608309949</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.629911314651256</v>
+        <v>1.613108105221861</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.134939912265542</v>
+        <v>0.1351427093768371</v>
       </c>
       <c r="C99">
-        <v>-18.59944862172517</v>
+        <v>-21.03945900692025</v>
       </c>
       <c r="D99">
-        <v>177.1065513782748</v>
+        <v>176.7045409930798</v>
       </c>
       <c r="E99">
-        <v>70.08600000000001</v>
+        <v>72.12400000000002</v>
       </c>
       <c r="F99">
-        <v>197.686</v>
+        <v>199.724</v>
       </c>
       <c r="G99">
         <v>1.98</v>
@@ -9533,28 +9533,28 @@
         <v>28.7</v>
       </c>
       <c r="M99">
-        <v>17.79174</v>
+        <v>17.97516</v>
       </c>
       <c r="N99">
-        <v>10.90826</v>
+        <v>10.72484</v>
       </c>
       <c r="O99">
-        <v>1.636239</v>
+        <v>1.608726</v>
       </c>
       <c r="P99">
-        <v>9.272021000000002</v>
+        <v>9.116114</v>
       </c>
       <c r="Q99">
-        <v>17.572021</v>
+        <v>17.416114</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.024497075518066</v>
+        <v>3.008635468841855</v>
       </c>
       <c r="T99">
-        <v>25.78905608309949</v>
+        <v>38.6156784766832</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.613108105221861</v>
+        <v>1.596647818433883</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1351427093768371</v>
+        <v>0.1353455064881323</v>
       </c>
       <c r="C100">
-        <v>-21.03945900692025</v>
+        <v>-23.47764849572363</v>
       </c>
       <c r="D100">
-        <v>176.7045409930798</v>
+        <v>176.3043515042764</v>
       </c>
       <c r="E100">
-        <v>72.12400000000002</v>
+        <v>74.16200000000001</v>
       </c>
       <c r="F100">
-        <v>199.724</v>
+        <v>201.762</v>
       </c>
       <c r="G100">
         <v>1.98</v>
@@ -9615,28 +9615,28 @@
         <v>28.7</v>
       </c>
       <c r="M100">
-        <v>17.97516</v>
+        <v>18.15858</v>
       </c>
       <c r="N100">
-        <v>10.72484</v>
+        <v>10.54142</v>
       </c>
       <c r="O100">
-        <v>1.608726</v>
+        <v>1.581213</v>
       </c>
       <c r="P100">
-        <v>9.116114</v>
+        <v>8.960207000000002</v>
       </c>
       <c r="Q100">
-        <v>17.416114</v>
+        <v>17.260207</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.008635468841855</v>
+        <v>5.961050648813222</v>
       </c>
       <c r="T100">
-        <v>38.6156784766832</v>
+        <v>77.09554565743433</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.596647818433883</v>
+        <v>1.580520062692127</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1353455064881323</v>
-      </c>
-      <c r="C101">
-        <v>-23.47764849572363</v>
-      </c>
-      <c r="D101">
-        <v>176.3043515042764</v>
-      </c>
-      <c r="E101">
-        <v>74.16200000000001</v>
-      </c>
-      <c r="F101">
-        <v>201.762</v>
-      </c>
-      <c r="G101">
-        <v>1.98</v>
-      </c>
-      <c r="H101">
-        <v>76.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>37</v>
-      </c>
-      <c r="K101">
-        <v>8.299999999999999</v>
-      </c>
-      <c r="L101">
-        <v>28.7</v>
-      </c>
-      <c r="M101">
-        <v>18.15858</v>
-      </c>
-      <c r="N101">
-        <v>10.54142</v>
-      </c>
-      <c r="O101">
-        <v>1.581213</v>
-      </c>
-      <c r="P101">
-        <v>8.960207000000002</v>
-      </c>
-      <c r="Q101">
-        <v>17.260207</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.961050648813222</v>
-      </c>
-      <c r="T101">
-        <v>77.09554565743433</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.0765</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.580520062692127</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
